--- a/evaluation/RQ7/generality_dataset.xlsx
+++ b/evaluation/RQ7/generality_dataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13317,7 +13317,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13328,13 +13328,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -13802,28 +13795,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -13832,118 +13828,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -14297,9 +14290,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H1074"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="21.8888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="16384" width="21.8888888888889" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -14327,7 +14323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" hidden="1" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -14353,7 +14349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" hidden="1" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -14379,7 +14375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" hidden="1" spans="1:8">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -14405,7 +14401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" hidden="1" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -14431,7 +14427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" hidden="1" spans="1:8">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -14457,7 +14453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" hidden="1" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -14483,7 +14479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" hidden="1" spans="1:8">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -14509,7 +14505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" hidden="1" spans="1:8">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -14535,7 +14531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" hidden="1" spans="1:8">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -14561,7 +14557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" hidden="1" spans="1:8">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -14587,7 +14583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" hidden="1" spans="1:8">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -14613,7 +14609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" hidden="1" spans="1:8">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -14639,7 +14635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" hidden="1" spans="1:8">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -14665,7 +14661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" hidden="1" spans="1:8">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -14691,7 +14687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" hidden="1" spans="1:8">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -14717,7 +14713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" hidden="1" spans="1:8">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -14743,7 +14739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" hidden="1" spans="1:8">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -14769,7 +14765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" hidden="1" spans="1:8">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -14795,7 +14791,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" hidden="1" spans="1:8">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -14821,7 +14817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" hidden="1" spans="1:8">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -14847,7 +14843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" hidden="1" spans="1:8">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -14873,7 +14869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" hidden="1" spans="1:8">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -14899,7 +14895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" hidden="1" spans="1:8">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -14925,7 +14921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" hidden="1" spans="1:8">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -14951,7 +14947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" hidden="1" spans="1:8">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -14977,7 +14973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" hidden="1" spans="1:8">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -15003,7 +14999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" hidden="1" spans="1:8">
       <c r="A28" t="s">
         <v>77</v>
       </c>
@@ -15029,7 +15025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" hidden="1" spans="1:8">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -15055,7 +15051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" hidden="1" spans="1:8">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -15081,7 +15077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" hidden="1" spans="1:8">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -15107,7 +15103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" hidden="1" spans="1:8">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -15133,7 +15129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" hidden="1" spans="1:8">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -15159,7 +15155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" hidden="1" spans="1:8">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -15185,7 +15181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" hidden="1" spans="1:8">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -15211,7 +15207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" hidden="1" spans="1:8">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -15237,7 +15233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" hidden="1" spans="1:8">
       <c r="A37" t="s">
         <v>101</v>
       </c>
@@ -15263,7 +15259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" hidden="1" spans="1:8">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -15289,7 +15285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" hidden="1" spans="1:8">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -15315,7 +15311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" hidden="1" spans="1:8">
       <c r="A40" t="s">
         <v>111</v>
       </c>
@@ -15341,7 +15337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" hidden="1" spans="1:8">
       <c r="A41" t="s">
         <v>111</v>
       </c>
@@ -15367,7 +15363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" hidden="1" spans="1:8">
       <c r="A42" t="s">
         <v>111</v>
       </c>
@@ -15393,7 +15389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" hidden="1" spans="1:8">
       <c r="A43" t="s">
         <v>111</v>
       </c>
@@ -15419,7 +15415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" hidden="1" spans="1:8">
       <c r="A44" t="s">
         <v>111</v>
       </c>
@@ -15445,7 +15441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" hidden="1" spans="1:8">
       <c r="A45" t="s">
         <v>130</v>
       </c>
@@ -15471,7 +15467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" hidden="1" spans="1:8">
       <c r="A46" t="s">
         <v>111</v>
       </c>
@@ -15497,7 +15493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" hidden="1" spans="1:8">
       <c r="A47" t="s">
         <v>130</v>
       </c>
@@ -15523,7 +15519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" hidden="1" spans="1:8">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -15575,7 +15571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" hidden="1" spans="1:8">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -15601,7 +15597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" hidden="1" spans="1:8">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -15653,7 +15649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" hidden="1" spans="1:8">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -15679,7 +15675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" hidden="1" spans="1:8">
       <c r="A54" t="s">
         <v>153</v>
       </c>
@@ -15705,7 +15701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" hidden="1" spans="1:8">
       <c r="A55" t="s">
         <v>156</v>
       </c>
@@ -15731,7 +15727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" hidden="1" spans="1:8">
       <c r="A56" t="s">
         <v>160</v>
       </c>
@@ -15757,7 +15753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" hidden="1" spans="1:8">
       <c r="A57" t="s">
         <v>148</v>
       </c>
@@ -15783,7 +15779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" hidden="1" spans="1:8">
       <c r="A58" t="s">
         <v>153</v>
       </c>
@@ -15809,7 +15805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" hidden="1" spans="1:8">
       <c r="A59" t="s">
         <v>165</v>
       </c>
@@ -15835,7 +15831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" hidden="1" spans="1:8">
       <c r="A60" t="s">
         <v>165</v>
       </c>
@@ -15861,7 +15857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" hidden="1" spans="1:8">
       <c r="A61" t="s">
         <v>165</v>
       </c>
@@ -15887,7 +15883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" hidden="1" spans="1:8">
       <c r="A62" t="s">
         <v>165</v>
       </c>
@@ -15913,7 +15909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" hidden="1" spans="1:8">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -15939,7 +15935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" hidden="1" spans="1:8">
       <c r="A64" t="s">
         <v>165</v>
       </c>
@@ -15965,7 +15961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" hidden="1" spans="1:8">
       <c r="A65" t="s">
         <v>176</v>
       </c>
@@ -15991,7 +15987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" hidden="1" spans="1:8">
       <c r="A66" t="s">
         <v>165</v>
       </c>
@@ -16017,7 +16013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" hidden="1" spans="1:8">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -16043,7 +16039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" hidden="1" spans="1:8">
       <c r="A68" t="s">
         <v>165</v>
       </c>
@@ -16069,7 +16065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" hidden="1" spans="1:8">
       <c r="A69" t="s">
         <v>176</v>
       </c>
@@ -16095,7 +16091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" hidden="1" spans="1:8">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -16121,7 +16117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" hidden="1" spans="1:8">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -16147,7 +16143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" hidden="1" spans="1:8">
       <c r="A72" t="s">
         <v>193</v>
       </c>
@@ -16173,7 +16169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" hidden="1" spans="1:8">
       <c r="A73" t="s">
         <v>176</v>
       </c>
@@ -16199,7 +16195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" hidden="1" spans="1:8">
       <c r="A74" t="s">
         <v>165</v>
       </c>
@@ -16225,7 +16221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" hidden="1" spans="1:8">
       <c r="A75" t="s">
         <v>190</v>
       </c>
@@ -16251,7 +16247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" hidden="1" spans="1:8">
       <c r="A76" t="s">
         <v>200</v>
       </c>
@@ -16277,7 +16273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" hidden="1" spans="1:8">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -16303,7 +16299,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" hidden="1" spans="1:8">
       <c r="A78" t="s">
         <v>209</v>
       </c>
@@ -16329,7 +16325,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" hidden="1" spans="1:8">
       <c r="A79" t="s">
         <v>204</v>
       </c>
@@ -16355,7 +16351,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" hidden="1" spans="1:8">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -16381,7 +16377,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" hidden="1" spans="1:8">
       <c r="A81" t="s">
         <v>204</v>
       </c>
@@ -16407,7 +16403,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" hidden="1" spans="1:8">
       <c r="A82" t="s">
         <v>209</v>
       </c>
@@ -16433,7 +16429,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" hidden="1" spans="1:8">
       <c r="A83" t="s">
         <v>204</v>
       </c>
@@ -16459,7 +16455,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" hidden="1" spans="1:8">
       <c r="A84" t="s">
         <v>209</v>
       </c>
@@ -16485,7 +16481,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" hidden="1" spans="1:8">
       <c r="A85" t="s">
         <v>204</v>
       </c>
@@ -16511,7 +16507,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" hidden="1" spans="1:8">
       <c r="A86" t="s">
         <v>209</v>
       </c>
@@ -16537,7 +16533,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" hidden="1" spans="1:8">
       <c r="A87" t="s">
         <v>204</v>
       </c>
@@ -16563,7 +16559,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" hidden="1" spans="1:8">
       <c r="A88" t="s">
         <v>209</v>
       </c>
@@ -16589,7 +16585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" hidden="1" spans="1:8">
       <c r="A89" t="s">
         <v>204</v>
       </c>
@@ -16615,7 +16611,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" hidden="1" spans="1:8">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -16641,7 +16637,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" hidden="1" spans="1:8">
       <c r="A91" t="s">
         <v>204</v>
       </c>
@@ -16667,7 +16663,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" hidden="1" spans="1:8">
       <c r="A92" t="s">
         <v>209</v>
       </c>
@@ -16693,7 +16689,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" hidden="1" spans="1:8">
       <c r="A93" t="s">
         <v>232</v>
       </c>
@@ -16719,7 +16715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" hidden="1" spans="1:8">
       <c r="A94" t="s">
         <v>232</v>
       </c>
@@ -16745,7 +16741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" hidden="1" spans="1:8">
       <c r="A95" t="s">
         <v>232</v>
       </c>
@@ -16771,7 +16767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" hidden="1" spans="1:8">
       <c r="A96" t="s">
         <v>232</v>
       </c>
@@ -16797,7 +16793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" hidden="1" spans="1:8">
       <c r="A97" t="s">
         <v>243</v>
       </c>
@@ -16823,7 +16819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" hidden="1" spans="1:8">
       <c r="A98" t="s">
         <v>243</v>
       </c>
@@ -16849,7 +16845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" hidden="1" spans="1:8">
       <c r="A99" t="s">
         <v>243</v>
       </c>
@@ -16875,7 +16871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" hidden="1" spans="1:8">
       <c r="A100" t="s">
         <v>252</v>
       </c>
@@ -16901,7 +16897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" hidden="1" spans="1:8">
       <c r="A101" t="s">
         <v>243</v>
       </c>
@@ -16927,7 +16923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" hidden="1" spans="1:8">
       <c r="A102" t="s">
         <v>252</v>
       </c>
@@ -16953,7 +16949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" hidden="1" spans="1:8">
       <c r="A103" t="s">
         <v>259</v>
       </c>
@@ -16979,7 +16975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" hidden="1" spans="1:8">
       <c r="A104" t="s">
         <v>243</v>
       </c>
@@ -17005,7 +17001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" hidden="1" spans="1:8">
       <c r="A105" t="s">
         <v>243</v>
       </c>
@@ -17031,7 +17027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" hidden="1" spans="1:8">
       <c r="A106" t="s">
         <v>200</v>
       </c>
@@ -17057,7 +17053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" hidden="1" spans="1:8">
       <c r="A107" t="s">
         <v>200</v>
       </c>
@@ -17083,7 +17079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" hidden="1" spans="1:8">
       <c r="A108" t="s">
         <v>270</v>
       </c>
@@ -17109,7 +17105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" hidden="1" spans="1:8">
       <c r="A109" t="s">
         <v>270</v>
       </c>
@@ -17135,7 +17131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" hidden="1" spans="1:8">
       <c r="A110" t="s">
         <v>270</v>
       </c>
@@ -17161,7 +17157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" hidden="1" spans="1:8">
       <c r="A111" t="s">
         <v>270</v>
       </c>
@@ -17187,7 +17183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" hidden="1" spans="1:8">
       <c r="A112" t="s">
         <v>282</v>
       </c>
@@ -17213,7 +17209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" hidden="1" spans="1:8">
       <c r="A113" t="s">
         <v>282</v>
       </c>
@@ -17239,7 +17235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" hidden="1" spans="1:8">
       <c r="A114" t="s">
         <v>282</v>
       </c>
@@ -17265,7 +17261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" hidden="1" spans="1:8">
       <c r="A115" t="s">
         <v>282</v>
       </c>
@@ -17291,7 +17287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" hidden="1" spans="1:8">
       <c r="A116" t="s">
         <v>282</v>
       </c>
@@ -17317,7 +17313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" hidden="1" spans="1:8">
       <c r="A117" t="s">
         <v>282</v>
       </c>
@@ -17343,7 +17339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" hidden="1" spans="1:8">
       <c r="A118" t="s">
         <v>282</v>
       </c>
@@ -17369,7 +17365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" hidden="1" spans="1:8">
       <c r="A119" t="s">
         <v>282</v>
       </c>
@@ -17395,7 +17391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" hidden="1" spans="1:8">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -17421,7 +17417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" hidden="1" spans="1:8">
       <c r="A121" t="s">
         <v>193</v>
       </c>
@@ -17447,7 +17443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" hidden="1" spans="1:8">
       <c r="A122" t="s">
         <v>193</v>
       </c>
@@ -17473,7 +17469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" hidden="1" spans="1:8">
       <c r="A123" t="s">
         <v>308</v>
       </c>
@@ -17499,7 +17495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" hidden="1" spans="1:8">
       <c r="A124" t="s">
         <v>308</v>
       </c>
@@ -17525,7 +17521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" hidden="1" spans="1:8">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -17551,7 +17547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" hidden="1" spans="1:8">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -17577,7 +17573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" hidden="1" spans="1:8">
       <c r="A127" t="s">
         <v>308</v>
       </c>
@@ -17603,7 +17599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" hidden="1" spans="1:8">
       <c r="A128" t="s">
         <v>308</v>
       </c>
@@ -17629,7 +17625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" hidden="1" spans="1:8">
       <c r="A129" t="s">
         <v>308</v>
       </c>
@@ -17655,7 +17651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" hidden="1" spans="1:8">
       <c r="A130" t="s">
         <v>308</v>
       </c>
@@ -17681,7 +17677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" hidden="1" spans="1:8">
       <c r="A131" t="s">
         <v>165</v>
       </c>
@@ -17707,7 +17703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" hidden="1" spans="1:8">
       <c r="A132" t="s">
         <v>165</v>
       </c>
@@ -17733,7 +17729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" hidden="1" spans="1:8">
       <c r="A133" t="s">
         <v>165</v>
       </c>
@@ -17759,7 +17755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" hidden="1" spans="1:8">
       <c r="A134" t="s">
         <v>176</v>
       </c>
@@ -17785,7 +17781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" hidden="1" spans="1:8">
       <c r="A135" t="s">
         <v>165</v>
       </c>
@@ -17811,7 +17807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" hidden="1" spans="1:8">
       <c r="A136" t="s">
         <v>176</v>
       </c>
@@ -17837,7 +17833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" hidden="1" spans="1:8">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -17863,7 +17859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" hidden="1" spans="1:8">
       <c r="A138" t="s">
         <v>176</v>
       </c>
@@ -17889,7 +17885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" hidden="1" spans="1:8">
       <c r="A139" t="s">
         <v>165</v>
       </c>
@@ -17915,7 +17911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" hidden="1" spans="1:8">
       <c r="A140" t="s">
         <v>176</v>
       </c>
@@ -17941,7 +17937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" hidden="1" spans="1:8">
       <c r="A141" t="s">
         <v>165</v>
       </c>
@@ -17967,7 +17963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" hidden="1" spans="1:8">
       <c r="A142" t="s">
         <v>259</v>
       </c>
@@ -17993,7 +17989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" hidden="1" spans="1:8">
       <c r="A143" t="s">
         <v>259</v>
       </c>
@@ -18019,7 +18015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" hidden="1" spans="1:8">
       <c r="A144" t="s">
         <v>259</v>
       </c>
@@ -18045,7 +18041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" hidden="1" spans="1:8">
       <c r="A145" t="s">
         <v>259</v>
       </c>
@@ -18071,7 +18067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" hidden="1" spans="1:8">
       <c r="A146" t="s">
         <v>259</v>
       </c>
@@ -18097,7 +18093,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" hidden="1" spans="1:8">
       <c r="A147" t="s">
         <v>259</v>
       </c>
@@ -18123,7 +18119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" hidden="1" spans="1:8">
       <c r="A148" t="s">
         <v>259</v>
       </c>
@@ -18149,7 +18145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" hidden="1" spans="1:8">
       <c r="A149" t="s">
         <v>259</v>
       </c>
@@ -18175,7 +18171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" hidden="1" spans="1:8">
       <c r="A150" t="s">
         <v>259</v>
       </c>
@@ -18201,7 +18197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" hidden="1" spans="1:8">
       <c r="A151" t="s">
         <v>259</v>
       </c>
@@ -18227,7 +18223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" hidden="1" spans="1:8">
       <c r="A152" t="s">
         <v>259</v>
       </c>
@@ -18253,7 +18249,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" hidden="1" spans="1:8">
       <c r="A153" t="s">
         <v>308</v>
       </c>
@@ -18279,7 +18275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" hidden="1" spans="1:8">
       <c r="A154" t="s">
         <v>370</v>
       </c>
@@ -18305,7 +18301,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" hidden="1" spans="1:8">
       <c r="A155" t="s">
         <v>373</v>
       </c>
@@ -18331,7 +18327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" hidden="1" spans="1:8">
       <c r="A156" t="s">
         <v>308</v>
       </c>
@@ -18357,7 +18353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" hidden="1" spans="1:8">
       <c r="A157" t="s">
         <v>370</v>
       </c>
@@ -18383,7 +18379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" hidden="1" spans="1:8">
       <c r="A158" t="s">
         <v>373</v>
       </c>
@@ -18409,7 +18405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" hidden="1" spans="1:8">
       <c r="A159" t="s">
         <v>308</v>
       </c>
@@ -18435,7 +18431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" hidden="1" spans="1:8">
       <c r="A160" t="s">
         <v>370</v>
       </c>
@@ -18461,7 +18457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" hidden="1" spans="1:8">
       <c r="A161" t="s">
         <v>373</v>
       </c>
@@ -18487,7 +18483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" hidden="1" spans="1:8">
       <c r="A162" t="s">
         <v>308</v>
       </c>
@@ -18513,7 +18509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" hidden="1" spans="1:8">
       <c r="A163" t="s">
         <v>370</v>
       </c>
@@ -18539,7 +18535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" hidden="1" spans="1:8">
       <c r="A164" t="s">
         <v>373</v>
       </c>
@@ -18565,7 +18561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" hidden="1" spans="1:8">
       <c r="A165" t="s">
         <v>308</v>
       </c>
@@ -18591,7 +18587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" hidden="1" spans="1:8">
       <c r="A166" t="s">
         <v>370</v>
       </c>
@@ -18617,7 +18613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" hidden="1" spans="1:8">
       <c r="A167" t="s">
         <v>373</v>
       </c>
@@ -18643,7 +18639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" hidden="1" spans="1:8">
       <c r="A168" t="s">
         <v>308</v>
       </c>
@@ -18669,7 +18665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" hidden="1" spans="1:8">
       <c r="A169" t="s">
         <v>370</v>
       </c>
@@ -18695,7 +18691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" hidden="1" spans="1:8">
       <c r="A170" t="s">
         <v>373</v>
       </c>
@@ -18721,7 +18717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" hidden="1" spans="1:8">
       <c r="A171" t="s">
         <v>308</v>
       </c>
@@ -18747,7 +18743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" hidden="1" spans="1:8">
       <c r="A172" t="s">
         <v>370</v>
       </c>
@@ -18773,7 +18769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" hidden="1" spans="1:8">
       <c r="A173" t="s">
         <v>373</v>
       </c>
@@ -18799,7 +18795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" hidden="1" spans="1:8">
       <c r="A174" t="s">
         <v>308</v>
       </c>
@@ -18825,7 +18821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" hidden="1" spans="1:8">
       <c r="A175" t="s">
         <v>370</v>
       </c>
@@ -18851,7 +18847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" hidden="1" spans="1:8">
       <c r="A176" t="s">
         <v>373</v>
       </c>
@@ -18877,7 +18873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" hidden="1" spans="1:8">
       <c r="A177" t="s">
         <v>308</v>
       </c>
@@ -18903,7 +18899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" hidden="1" spans="1:8">
       <c r="A178" t="s">
         <v>405</v>
       </c>
@@ -18929,7 +18925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" hidden="1" spans="1:8">
       <c r="A179" t="s">
         <v>405</v>
       </c>
@@ -18955,7 +18951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" hidden="1" spans="1:8">
       <c r="A180" t="s">
         <v>405</v>
       </c>
@@ -18981,7 +18977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" hidden="1" spans="1:8">
       <c r="A181" t="s">
         <v>405</v>
       </c>
@@ -19007,7 +19003,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" hidden="1" spans="1:8">
       <c r="A182" t="s">
         <v>405</v>
       </c>
@@ -19033,7 +19029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" hidden="1" spans="1:8">
       <c r="A183" t="s">
         <v>405</v>
       </c>
@@ -19059,7 +19055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" hidden="1" spans="1:8">
       <c r="A184" t="s">
         <v>405</v>
       </c>
@@ -19085,7 +19081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" hidden="1" spans="1:8">
       <c r="A185" t="s">
         <v>422</v>
       </c>
@@ -19111,7 +19107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" hidden="1" spans="1:8">
       <c r="A186" t="s">
         <v>427</v>
       </c>
@@ -19137,7 +19133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" hidden="1" spans="1:8">
       <c r="A187" t="s">
         <v>427</v>
       </c>
@@ -19163,7 +19159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" hidden="1" spans="1:8">
       <c r="A188" t="s">
         <v>427</v>
       </c>
@@ -19189,7 +19185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" hidden="1" spans="1:8">
       <c r="A189" t="s">
         <v>436</v>
       </c>
@@ -19215,7 +19211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" hidden="1" spans="1:8">
       <c r="A190" t="s">
         <v>441</v>
       </c>
@@ -19241,7 +19237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" hidden="1" spans="1:8">
       <c r="A191" t="s">
         <v>443</v>
       </c>
@@ -19267,7 +19263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" hidden="1" spans="1:8">
       <c r="A192" t="s">
         <v>443</v>
       </c>
@@ -19293,7 +19289,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" hidden="1" spans="1:8">
       <c r="A193" t="s">
         <v>443</v>
       </c>
@@ -19319,7 +19315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" hidden="1" spans="1:8">
       <c r="A194" t="s">
         <v>443</v>
       </c>
@@ -19345,7 +19341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" hidden="1" spans="1:8">
       <c r="A195" t="s">
         <v>443</v>
       </c>
@@ -19371,7 +19367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" hidden="1" spans="1:8">
       <c r="A196" t="s">
         <v>443</v>
       </c>
@@ -19397,7 +19393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" hidden="1" spans="1:8">
       <c r="A197" t="s">
         <v>443</v>
       </c>
@@ -19423,7 +19419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" hidden="1" spans="1:8">
       <c r="A198" t="s">
         <v>461</v>
       </c>
@@ -19449,7 +19445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" hidden="1" spans="1:8">
       <c r="A199" t="s">
         <v>461</v>
       </c>
@@ -19475,7 +19471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" hidden="1" spans="1:8">
       <c r="A200" t="s">
         <v>468</v>
       </c>
@@ -19501,7 +19497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" hidden="1" spans="1:8">
       <c r="A201" t="s">
         <v>474</v>
       </c>
@@ -19527,7 +19523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" hidden="1" spans="1:8">
       <c r="A202" t="s">
         <v>479</v>
       </c>
@@ -19553,7 +19549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" hidden="1" spans="1:8">
       <c r="A203" t="s">
         <v>474</v>
       </c>
@@ -19579,7 +19575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" hidden="1" spans="1:8">
       <c r="A204" t="s">
         <v>479</v>
       </c>
@@ -19605,7 +19601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" hidden="1" spans="1:8">
       <c r="A205" t="s">
         <v>474</v>
       </c>
@@ -19631,7 +19627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" hidden="1" spans="1:8">
       <c r="A206" t="s">
         <v>479</v>
       </c>
@@ -19657,7 +19653,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" hidden="1" spans="1:8">
       <c r="A207" t="s">
         <v>308</v>
       </c>
@@ -19683,7 +19679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" hidden="1" spans="1:8">
       <c r="A208" t="s">
         <v>308</v>
       </c>
@@ -19709,7 +19705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" hidden="1" spans="1:8">
       <c r="A209" t="s">
         <v>308</v>
       </c>
@@ -19735,7 +19731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" hidden="1" spans="1:8">
       <c r="A210" t="s">
         <v>308</v>
       </c>
@@ -19761,7 +19757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" hidden="1" spans="1:8">
       <c r="A211" t="s">
         <v>308</v>
       </c>
@@ -19787,7 +19783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" hidden="1" spans="1:8">
       <c r="A212" t="s">
         <v>308</v>
       </c>
@@ -19813,7 +19809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" hidden="1" spans="1:8">
       <c r="A213" t="s">
         <v>308</v>
       </c>
@@ -19839,7 +19835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" hidden="1" spans="1:8">
       <c r="A214" t="s">
         <v>308</v>
       </c>
@@ -19865,7 +19861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" hidden="1" spans="1:8">
       <c r="A215" t="s">
         <v>308</v>
       </c>
@@ -19891,7 +19887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" hidden="1" spans="1:8">
       <c r="A216" t="s">
         <v>308</v>
       </c>
@@ -19917,7 +19913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" hidden="1" spans="1:8">
       <c r="A217" t="s">
         <v>308</v>
       </c>
@@ -19943,7 +19939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" hidden="1" spans="1:8">
       <c r="A218" t="s">
         <v>308</v>
       </c>
@@ -19969,7 +19965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" hidden="1" spans="1:8">
       <c r="A219" t="s">
         <v>512</v>
       </c>
@@ -19995,7 +19991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" hidden="1" spans="1:8">
       <c r="A220" t="s">
         <v>512</v>
       </c>
@@ -20021,7 +20017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" hidden="1" spans="1:8">
       <c r="A221" t="s">
         <v>520</v>
       </c>
@@ -20047,7 +20043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" hidden="1" spans="1:8">
       <c r="A222" t="s">
         <v>520</v>
       </c>
@@ -20073,7 +20069,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" hidden="1" spans="1:8">
       <c r="A223" t="s">
         <v>527</v>
       </c>
@@ -20099,7 +20095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" hidden="1" spans="1:8">
       <c r="A224" t="s">
         <v>520</v>
       </c>
@@ -20125,7 +20121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" hidden="1" spans="1:8">
       <c r="A225" t="s">
         <v>527</v>
       </c>
@@ -20151,7 +20147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" hidden="1" spans="1:8">
       <c r="A226" t="s">
         <v>532</v>
       </c>
@@ -20177,7 +20173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" hidden="1" spans="1:8">
       <c r="A227" t="s">
         <v>520</v>
       </c>
@@ -20203,7 +20199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" hidden="1" spans="1:8">
       <c r="A228" t="s">
         <v>527</v>
       </c>
@@ -20229,7 +20225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" hidden="1" spans="1:8">
       <c r="A229" t="s">
         <v>532</v>
       </c>
@@ -20255,7 +20251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" hidden="1" spans="1:8">
       <c r="A230" t="s">
         <v>539</v>
       </c>
@@ -20281,7 +20277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" hidden="1" spans="1:8">
       <c r="A231" t="s">
         <v>542</v>
       </c>
@@ -20307,7 +20303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" hidden="1" spans="1:8">
       <c r="A232" t="s">
         <v>520</v>
       </c>
@@ -20333,7 +20329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" hidden="1" spans="1:8">
       <c r="A233" t="s">
         <v>545</v>
       </c>
@@ -20359,7 +20355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" hidden="1" spans="1:8">
       <c r="A234" t="s">
         <v>527</v>
       </c>
@@ -20385,7 +20381,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" hidden="1" spans="1:8">
       <c r="A235" t="s">
         <v>548</v>
       </c>
@@ -20411,7 +20407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" hidden="1" spans="1:8">
       <c r="A236" t="s">
         <v>550</v>
       </c>
@@ -20437,7 +20433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" hidden="1" spans="1:8">
       <c r="A237" t="s">
         <v>552</v>
       </c>
@@ -20463,7 +20459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" hidden="1" spans="1:8">
       <c r="A238" t="s">
         <v>554</v>
       </c>
@@ -20489,7 +20485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" hidden="1" spans="1:8">
       <c r="A239" t="s">
         <v>556</v>
       </c>
@@ -20515,7 +20511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" hidden="1" spans="1:8">
       <c r="A240" t="s">
         <v>532</v>
       </c>
@@ -20541,7 +20537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" hidden="1" spans="1:8">
       <c r="A241" t="s">
         <v>559</v>
       </c>
@@ -20567,7 +20563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" hidden="1" spans="1:8">
       <c r="A242" t="s">
         <v>559</v>
       </c>
@@ -20593,7 +20589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" hidden="1" spans="1:8">
       <c r="A243" t="s">
         <v>559</v>
       </c>
@@ -20619,7 +20615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" hidden="1" spans="1:8">
       <c r="A244" t="s">
         <v>559</v>
       </c>
@@ -20645,7 +20641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" hidden="1" spans="1:8">
       <c r="A245" t="s">
         <v>559</v>
       </c>
@@ -20671,7 +20667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" hidden="1" spans="1:8">
       <c r="A246" t="s">
         <v>559</v>
       </c>
@@ -20697,7 +20693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" hidden="1" spans="1:8">
       <c r="A247" t="s">
         <v>559</v>
       </c>
@@ -20723,7 +20719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" hidden="1" spans="1:8">
       <c r="A248" t="s">
         <v>559</v>
       </c>
@@ -20749,7 +20745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" hidden="1" spans="1:8">
       <c r="A249" t="s">
         <v>578</v>
       </c>
@@ -20775,7 +20771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" hidden="1" spans="1:8">
       <c r="A250" t="s">
         <v>578</v>
       </c>
@@ -20801,7 +20797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" hidden="1" spans="1:8">
       <c r="A251" t="s">
         <v>578</v>
       </c>
@@ -20827,7 +20823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" hidden="1" spans="1:8">
       <c r="A252" t="s">
         <v>578</v>
       </c>
@@ -20853,7 +20849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" hidden="1" spans="1:8">
       <c r="A253" t="s">
         <v>589</v>
       </c>
@@ -20879,7 +20875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" hidden="1" spans="1:8">
       <c r="A254" t="s">
         <v>589</v>
       </c>
@@ -20905,7 +20901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" hidden="1" spans="1:8">
       <c r="A255" t="s">
         <v>589</v>
       </c>
@@ -20931,7 +20927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" hidden="1" spans="1:8">
       <c r="A256" t="s">
         <v>589</v>
       </c>
@@ -20957,7 +20953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" hidden="1" spans="1:8">
       <c r="A257" t="s">
         <v>589</v>
       </c>
@@ -20983,7 +20979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" hidden="1" spans="1:8">
       <c r="A258" t="s">
         <v>589</v>
       </c>
@@ -21009,7 +21005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" hidden="1" spans="1:8">
       <c r="A259" t="s">
         <v>604</v>
       </c>
@@ -21035,7 +21031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" hidden="1" spans="1:8">
       <c r="A260" t="s">
         <v>589</v>
       </c>
@@ -21061,7 +21057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" hidden="1" spans="1:8">
       <c r="A261" t="s">
         <v>604</v>
       </c>
@@ -21087,7 +21083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" hidden="1" spans="1:8">
       <c r="A262" t="s">
         <v>589</v>
       </c>
@@ -21113,7 +21109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" hidden="1" spans="1:8">
       <c r="A263" t="s">
         <v>604</v>
       </c>
@@ -21139,7 +21135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" hidden="1" spans="1:8">
       <c r="A264" t="s">
         <v>612</v>
       </c>
@@ -21165,7 +21161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" hidden="1" spans="1:8">
       <c r="A265" t="s">
         <v>612</v>
       </c>
@@ -21191,7 +21187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" hidden="1" spans="1:8">
       <c r="A266" t="s">
         <v>252</v>
       </c>
@@ -21217,7 +21213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" hidden="1" spans="1:8">
       <c r="A267" t="s">
         <v>622</v>
       </c>
@@ -21243,7 +21239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" hidden="1" spans="1:8">
       <c r="A268" t="s">
         <v>622</v>
       </c>
@@ -21269,7 +21265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" hidden="1" spans="1:8">
       <c r="A269" t="s">
         <v>629</v>
       </c>
@@ -21295,7 +21291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" hidden="1" spans="1:8">
       <c r="A270" t="s">
         <v>622</v>
       </c>
@@ -21321,7 +21317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" hidden="1" spans="1:8">
       <c r="A271" t="s">
         <v>629</v>
       </c>
@@ -21347,7 +21343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" hidden="1" spans="1:8">
       <c r="A272" t="s">
         <v>635</v>
       </c>
@@ -21373,7 +21369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" hidden="1" spans="1:8">
       <c r="A273" t="s">
         <v>640</v>
       </c>
@@ -21399,7 +21395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" hidden="1" spans="1:8">
       <c r="A274" t="s">
         <v>640</v>
       </c>
@@ -21425,7 +21421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" hidden="1" spans="1:8">
       <c r="A275" t="s">
         <v>640</v>
       </c>
@@ -21451,7 +21447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" hidden="1" spans="1:8">
       <c r="A276" t="s">
         <v>640</v>
       </c>
@@ -21477,7 +21473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" hidden="1" spans="1:8">
       <c r="A277" t="s">
         <v>651</v>
       </c>
@@ -21503,7 +21499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" hidden="1" spans="1:8">
       <c r="A278" t="s">
         <v>651</v>
       </c>
@@ -21529,7 +21525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" hidden="1" spans="1:8">
       <c r="A279" t="s">
         <v>651</v>
       </c>
@@ -21555,7 +21551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" hidden="1" spans="1:8">
       <c r="A280" t="s">
         <v>651</v>
       </c>
@@ -21581,7 +21577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" hidden="1" spans="1:8">
       <c r="A281" t="s">
         <v>651</v>
       </c>
@@ -21607,7 +21603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" hidden="1" spans="1:8">
       <c r="A282" t="s">
         <v>651</v>
       </c>
@@ -21633,7 +21629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" hidden="1" spans="1:8">
       <c r="A283" t="s">
         <v>308</v>
       </c>
@@ -21659,7 +21655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" hidden="1" spans="1:8">
       <c r="A284" t="s">
         <v>668</v>
       </c>
@@ -21685,7 +21681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" hidden="1" spans="1:8">
       <c r="A285" t="s">
         <v>308</v>
       </c>
@@ -21711,7 +21707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" hidden="1" spans="1:8">
       <c r="A286" t="s">
         <v>668</v>
       </c>
@@ -21737,7 +21733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" hidden="1" spans="1:8">
       <c r="A287" t="s">
         <v>308</v>
       </c>
@@ -21763,7 +21759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" hidden="1" spans="1:8">
       <c r="A288" t="s">
         <v>668</v>
       </c>
@@ -21789,7 +21785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" hidden="1" spans="1:8">
       <c r="A289" t="s">
         <v>308</v>
       </c>
@@ -21815,7 +21811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" hidden="1" spans="1:8">
       <c r="A290" t="s">
         <v>668</v>
       </c>
@@ -21841,7 +21837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" hidden="1" spans="1:8">
       <c r="A291" t="s">
         <v>308</v>
       </c>
@@ -21867,7 +21863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" hidden="1" spans="1:8">
       <c r="A292" t="s">
         <v>668</v>
       </c>
@@ -21893,7 +21889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" hidden="1" spans="1:8">
       <c r="A293" t="s">
         <v>308</v>
       </c>
@@ -21919,7 +21915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" hidden="1" spans="1:8">
       <c r="A294" t="s">
         <v>668</v>
       </c>
@@ -21945,7 +21941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" hidden="1" spans="1:8">
       <c r="A295" t="s">
         <v>308</v>
       </c>
@@ -21971,7 +21967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" hidden="1" spans="1:8">
       <c r="A296" t="s">
         <v>668</v>
       </c>
@@ -21997,7 +21993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" hidden="1" spans="1:8">
       <c r="A297" t="s">
         <v>308</v>
       </c>
@@ -22023,7 +22019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" hidden="1" spans="1:8">
       <c r="A298" t="s">
         <v>668</v>
       </c>
@@ -22049,7 +22045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" hidden="1" spans="1:8">
       <c r="A299" t="s">
         <v>308</v>
       </c>
@@ -22075,7 +22071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" hidden="1" spans="1:8">
       <c r="A300" t="s">
         <v>668</v>
       </c>
@@ -22101,7 +22097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" hidden="1" spans="1:8">
       <c r="A301" t="s">
         <v>308</v>
       </c>
@@ -22127,7 +22123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" hidden="1" spans="1:8">
       <c r="A302" t="s">
         <v>668</v>
       </c>
@@ -22153,7 +22149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" hidden="1" spans="1:8">
       <c r="A303" t="s">
         <v>308</v>
       </c>
@@ -22179,7 +22175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" hidden="1" spans="1:8">
       <c r="A304" t="s">
         <v>668</v>
       </c>
@@ -22205,7 +22201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" hidden="1" spans="1:8">
       <c r="A305" t="s">
         <v>308</v>
       </c>
@@ -22231,7 +22227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" hidden="1" spans="1:8">
       <c r="A306" t="s">
         <v>668</v>
       </c>
@@ -22257,7 +22253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" hidden="1" spans="1:8">
       <c r="A307" t="s">
         <v>308</v>
       </c>
@@ -22283,7 +22279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" hidden="1" spans="1:8">
       <c r="A308" t="s">
         <v>668</v>
       </c>
@@ -22309,7 +22305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" hidden="1" spans="1:8">
       <c r="A309" t="s">
         <v>707</v>
       </c>
@@ -22335,7 +22331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" hidden="1" spans="1:8">
       <c r="A310" t="s">
         <v>712</v>
       </c>
@@ -22361,7 +22357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" hidden="1" spans="1:8">
       <c r="A311" t="s">
         <v>712</v>
       </c>
@@ -22387,7 +22383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" hidden="1" spans="1:8">
       <c r="A312" t="s">
         <v>719</v>
       </c>
@@ -22413,7 +22409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" hidden="1" spans="1:8">
       <c r="A313" t="s">
         <v>724</v>
       </c>
@@ -22439,7 +22435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" hidden="1" spans="1:8">
       <c r="A314" t="s">
         <v>719</v>
       </c>
@@ -22465,7 +22461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" hidden="1" spans="1:8">
       <c r="A315" t="s">
         <v>724</v>
       </c>
@@ -22491,7 +22487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" hidden="1" spans="1:8">
       <c r="A316" t="s">
         <v>719</v>
       </c>
@@ -22517,7 +22513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" hidden="1" spans="1:8">
       <c r="A317" t="s">
         <v>724</v>
       </c>
@@ -22543,7 +22539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" hidden="1" spans="1:8">
       <c r="A318" t="s">
         <v>719</v>
       </c>
@@ -22569,7 +22565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" hidden="1" spans="1:8">
       <c r="A319" t="s">
         <v>724</v>
       </c>
@@ -22595,7 +22591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" hidden="1" spans="1:8">
       <c r="A320" t="s">
         <v>736</v>
       </c>
@@ -22621,7 +22617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" hidden="1" spans="1:8">
       <c r="A321" t="s">
         <v>741</v>
       </c>
@@ -22647,7 +22643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" hidden="1" spans="1:8">
       <c r="A322" t="s">
         <v>741</v>
       </c>
@@ -22673,7 +22669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" hidden="1" spans="1:8">
       <c r="A323" t="s">
         <v>741</v>
       </c>
@@ -22699,7 +22695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" hidden="1" spans="1:8">
       <c r="A324" t="s">
         <v>741</v>
       </c>
@@ -22725,7 +22721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" hidden="1" spans="1:8">
       <c r="A325" t="s">
         <v>741</v>
       </c>
@@ -22751,7 +22747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" hidden="1" spans="1:8">
       <c r="A326" t="s">
         <v>741</v>
       </c>
@@ -22777,7 +22773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" hidden="1" spans="1:8">
       <c r="A327" t="s">
         <v>741</v>
       </c>
@@ -22803,7 +22799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" hidden="1" spans="1:8">
       <c r="A328" t="s">
         <v>741</v>
       </c>
@@ -22829,7 +22825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" hidden="1" spans="1:8">
       <c r="A329" t="s">
         <v>741</v>
       </c>
@@ -22855,7 +22851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" hidden="1" spans="1:8">
       <c r="A330" t="s">
         <v>760</v>
       </c>
@@ -22881,7 +22877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" hidden="1" spans="1:8">
       <c r="A331" t="s">
         <v>760</v>
       </c>
@@ -22907,7 +22903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" hidden="1" spans="1:8">
       <c r="A332" t="s">
         <v>760</v>
       </c>
@@ -22933,7 +22929,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" hidden="1" spans="1:8">
       <c r="A333" t="s">
         <v>760</v>
       </c>
@@ -22959,7 +22955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" hidden="1" spans="1:8">
       <c r="A334" t="s">
         <v>771</v>
       </c>
@@ -22985,7 +22981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" hidden="1" spans="1:8">
       <c r="A335" t="s">
         <v>771</v>
       </c>
@@ -23011,7 +23007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" hidden="1" spans="1:8">
       <c r="A336" t="s">
         <v>778</v>
       </c>
@@ -23037,7 +23033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" hidden="1" spans="1:8">
       <c r="A337" t="s">
         <v>778</v>
       </c>
@@ -23063,7 +23059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" hidden="1" spans="1:8">
       <c r="A338" t="s">
         <v>778</v>
       </c>
@@ -23089,7 +23085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" hidden="1" spans="1:8">
       <c r="A339" t="s">
         <v>778</v>
       </c>
@@ -23115,7 +23111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" hidden="1" spans="1:8">
       <c r="A340" t="s">
         <v>778</v>
       </c>
@@ -23141,7 +23137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" hidden="1" spans="1:8">
       <c r="A341" t="s">
         <v>778</v>
       </c>
@@ -23167,7 +23163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" hidden="1" spans="1:8">
       <c r="A342" t="s">
         <v>778</v>
       </c>
@@ -23193,7 +23189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" hidden="1" spans="1:8">
       <c r="A343" t="s">
         <v>778</v>
       </c>
@@ -23219,7 +23215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" hidden="1" spans="1:8">
       <c r="A344" t="s">
         <v>778</v>
       </c>
@@ -23245,7 +23241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" hidden="1" spans="1:8">
       <c r="A345" t="s">
         <v>778</v>
       </c>
@@ -23271,7 +23267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" hidden="1" spans="1:8">
       <c r="A346" t="s">
         <v>778</v>
       </c>
@@ -23297,7 +23293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" hidden="1" spans="1:8">
       <c r="A347" t="s">
         <v>778</v>
       </c>
@@ -23323,7 +23319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" hidden="1" spans="1:8">
       <c r="A348" t="s">
         <v>778</v>
       </c>
@@ -23349,7 +23345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" hidden="1" spans="1:8">
       <c r="A349" t="s">
         <v>778</v>
       </c>
@@ -23375,7 +23371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" hidden="1" spans="1:8">
       <c r="A350" t="s">
         <v>778</v>
       </c>
@@ -23401,7 +23397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" hidden="1" spans="1:8">
       <c r="A351" t="s">
         <v>811</v>
       </c>
@@ -23427,7 +23423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" hidden="1" spans="1:8">
       <c r="A352" t="s">
         <v>816</v>
       </c>
@@ -23453,7 +23449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" hidden="1" spans="1:8">
       <c r="A353" t="s">
         <v>811</v>
       </c>
@@ -23479,7 +23475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" hidden="1" spans="1:8">
       <c r="A354" t="s">
         <v>823</v>
       </c>
@@ -23505,7 +23501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" hidden="1" spans="1:8">
       <c r="A355" t="s">
         <v>823</v>
       </c>
@@ -23531,7 +23527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" hidden="1" spans="1:8">
       <c r="A356" t="s">
         <v>823</v>
       </c>
@@ -23557,7 +23553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" hidden="1" spans="1:8">
       <c r="A357" t="s">
         <v>823</v>
       </c>
@@ -23583,7 +23579,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" hidden="1" spans="1:8">
       <c r="A358" t="s">
         <v>823</v>
       </c>
@@ -23609,7 +23605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" hidden="1" spans="1:8">
       <c r="A359" t="s">
         <v>823</v>
       </c>
@@ -23635,7 +23631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" hidden="1" spans="1:8">
       <c r="A360" t="s">
         <v>823</v>
       </c>
@@ -23661,7 +23657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" hidden="1" spans="1:8">
       <c r="A361" t="s">
         <v>840</v>
       </c>
@@ -23687,7 +23683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" hidden="1" spans="1:8">
       <c r="A362" t="s">
         <v>840</v>
       </c>
@@ -23713,7 +23709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" hidden="1" spans="1:8">
       <c r="A363" t="s">
         <v>840</v>
       </c>
@@ -23739,7 +23735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" hidden="1" spans="1:8">
       <c r="A364" t="s">
         <v>840</v>
       </c>
@@ -23765,7 +23761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" hidden="1" spans="1:8">
       <c r="A365" t="s">
         <v>840</v>
       </c>
@@ -23791,7 +23787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" hidden="1" spans="1:8">
       <c r="A366" t="s">
         <v>840</v>
       </c>
@@ -23817,7 +23813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" hidden="1" spans="1:8">
       <c r="A367" t="s">
         <v>840</v>
       </c>
@@ -23843,7 +23839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" hidden="1" spans="1:8">
       <c r="A368" t="s">
         <v>8</v>
       </c>
@@ -23869,7 +23865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" hidden="1" spans="1:8">
       <c r="A369" t="s">
         <v>8</v>
       </c>
@@ -23895,7 +23891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" hidden="1" spans="1:8">
       <c r="A370" t="s">
         <v>18</v>
       </c>
@@ -23921,7 +23917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" hidden="1" spans="1:8">
       <c r="A371" t="s">
         <v>8</v>
       </c>
@@ -23947,7 +23943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" hidden="1" spans="1:8">
       <c r="A372" t="s">
         <v>18</v>
       </c>
@@ -23973,7 +23969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" hidden="1" spans="1:8">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -23999,7 +23995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" hidden="1" spans="1:8">
       <c r="A374" t="s">
         <v>18</v>
       </c>
@@ -24025,7 +24021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" hidden="1" spans="1:8">
       <c r="A375" t="s">
         <v>8</v>
       </c>
@@ -24051,7 +24047,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" hidden="1" spans="1:8">
       <c r="A376" t="s">
         <v>866</v>
       </c>
@@ -24077,7 +24073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" hidden="1" spans="1:8">
       <c r="A377" t="s">
         <v>866</v>
       </c>
@@ -24103,7 +24099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" hidden="1" spans="1:8">
       <c r="A378" t="s">
         <v>866</v>
       </c>
@@ -24129,7 +24125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" hidden="1" spans="1:8">
       <c r="A379" t="s">
         <v>866</v>
       </c>
@@ -24155,7 +24151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" spans="1:8">
+    <row r="380" hidden="1" spans="1:8">
       <c r="A380" t="s">
         <v>877</v>
       </c>
@@ -24181,7 +24177,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="381" spans="1:8">
+    <row r="381" hidden="1" spans="1:8">
       <c r="A381" t="s">
         <v>877</v>
       </c>
@@ -24207,7 +24203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" hidden="1" spans="1:8">
       <c r="A382" t="s">
         <v>877</v>
       </c>
@@ -24233,7 +24229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" hidden="1" spans="1:8">
       <c r="A383" t="s">
         <v>877</v>
       </c>
@@ -24259,7 +24255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" hidden="1" spans="1:8">
       <c r="A384" t="s">
         <v>877</v>
       </c>
@@ -24285,7 +24281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" hidden="1" spans="1:8">
       <c r="A385" t="s">
         <v>877</v>
       </c>
@@ -24311,7 +24307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" hidden="1" spans="1:8">
       <c r="A386" t="s">
         <v>877</v>
       </c>
@@ -24337,7 +24333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="387" spans="1:8">
+    <row r="387" hidden="1" spans="1:8">
       <c r="A387" t="s">
         <v>877</v>
       </c>
@@ -24363,7 +24359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" hidden="1" spans="1:8">
       <c r="A388" t="s">
         <v>877</v>
       </c>
@@ -24389,7 +24385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="389" spans="1:8">
+    <row r="389" hidden="1" spans="1:8">
       <c r="A389" t="s">
         <v>877</v>
       </c>
@@ -24415,7 +24411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="390" spans="1:8">
+    <row r="390" hidden="1" spans="1:8">
       <c r="A390" t="s">
         <v>877</v>
       </c>
@@ -24441,7 +24437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" hidden="1" spans="1:8">
       <c r="A391" t="s">
         <v>877</v>
       </c>
@@ -24467,7 +24463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" hidden="1" spans="1:8">
       <c r="A392" t="s">
         <v>877</v>
       </c>
@@ -24493,7 +24489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" hidden="1" spans="1:8">
       <c r="A393" t="s">
         <v>877</v>
       </c>
@@ -24519,7 +24515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="394" spans="1:8">
+    <row r="394" hidden="1" spans="1:8">
       <c r="A394" t="s">
         <v>877</v>
       </c>
@@ -24545,7 +24541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" hidden="1" spans="1:8">
       <c r="A395" t="s">
         <v>877</v>
       </c>
@@ -24571,7 +24567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" hidden="1" spans="1:8">
       <c r="A396" t="s">
         <v>877</v>
       </c>
@@ -24597,7 +24593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="397" spans="1:8">
+    <row r="397" hidden="1" spans="1:8">
       <c r="A397" t="s">
         <v>877</v>
       </c>
@@ -24623,7 +24619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="398" spans="1:8">
+    <row r="398" hidden="1" spans="1:8">
       <c r="A398" t="s">
         <v>877</v>
       </c>
@@ -24649,7 +24645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" hidden="1" spans="1:8">
       <c r="A399" t="s">
         <v>877</v>
       </c>
@@ -24675,7 +24671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" hidden="1" spans="1:8">
       <c r="A400" t="s">
         <v>877</v>
       </c>
@@ -24701,7 +24697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" hidden="1" spans="1:8">
       <c r="A401" t="s">
         <v>877</v>
       </c>
@@ -24727,7 +24723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" hidden="1" spans="1:8">
       <c r="A402" t="s">
         <v>877</v>
       </c>
@@ -24753,7 +24749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" hidden="1" spans="1:8">
       <c r="A403" t="s">
         <v>877</v>
       </c>
@@ -24779,7 +24775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" hidden="1" spans="1:8">
       <c r="A404" t="s">
         <v>877</v>
       </c>
@@ -24805,7 +24801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" hidden="1" spans="1:8">
       <c r="A405" t="s">
         <v>877</v>
       </c>
@@ -24831,7 +24827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" hidden="1" spans="1:8">
       <c r="A406" t="s">
         <v>877</v>
       </c>
@@ -24857,7 +24853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" hidden="1" spans="1:8">
       <c r="A407" t="s">
         <v>877</v>
       </c>
@@ -24883,7 +24879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" hidden="1" spans="1:8">
       <c r="A408" t="s">
         <v>405</v>
       </c>
@@ -24909,7 +24905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" hidden="1" spans="1:8">
       <c r="A409" t="s">
         <v>405</v>
       </c>
@@ -24935,7 +24931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" hidden="1" spans="1:8">
       <c r="A410" t="s">
         <v>943</v>
       </c>
@@ -24961,7 +24957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" hidden="1" spans="1:8">
       <c r="A411" t="s">
         <v>943</v>
       </c>
@@ -24987,7 +24983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" hidden="1" spans="1:8">
       <c r="A412" t="s">
         <v>943</v>
       </c>
@@ -25013,7 +25009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" hidden="1" spans="1:8">
       <c r="A413" t="s">
         <v>952</v>
       </c>
@@ -25039,7 +25035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" hidden="1" spans="1:8">
       <c r="A414" t="s">
         <v>548</v>
       </c>
@@ -25065,7 +25061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" hidden="1" spans="1:8">
       <c r="A415" t="s">
         <v>554</v>
       </c>
@@ -25091,7 +25087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" hidden="1" spans="1:8">
       <c r="A416" t="s">
         <v>552</v>
       </c>
@@ -25117,7 +25113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" hidden="1" spans="1:8">
       <c r="A417" t="s">
         <v>550</v>
       </c>
@@ -25143,7 +25139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" hidden="1" spans="1:8">
       <c r="A418" t="s">
         <v>542</v>
       </c>
@@ -25169,7 +25165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" hidden="1" spans="1:8">
       <c r="A419" t="s">
         <v>556</v>
       </c>
@@ -25195,7 +25191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" hidden="1" spans="1:8">
       <c r="A420" t="s">
         <v>545</v>
       </c>
@@ -25221,7 +25217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="421" spans="1:8">
+    <row r="421" hidden="1" spans="1:8">
       <c r="A421" t="s">
         <v>539</v>
       </c>
@@ -25247,7 +25243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="422" spans="1:8">
+    <row r="422" hidden="1" spans="1:8">
       <c r="A422" t="s">
         <v>532</v>
       </c>
@@ -25273,7 +25269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="423" spans="1:8">
+    <row r="423" hidden="1" spans="1:8">
       <c r="A423" t="s">
         <v>548</v>
       </c>
@@ -25299,7 +25295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="424" spans="1:8">
+    <row r="424" hidden="1" spans="1:8">
       <c r="A424" t="s">
         <v>554</v>
       </c>
@@ -25325,7 +25321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="425" spans="1:8">
+    <row r="425" hidden="1" spans="1:8">
       <c r="A425" t="s">
         <v>552</v>
       </c>
@@ -25351,7 +25347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="426" spans="1:8">
+    <row r="426" hidden="1" spans="1:8">
       <c r="A426" t="s">
         <v>550</v>
       </c>
@@ -25377,7 +25373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="427" spans="1:8">
+    <row r="427" hidden="1" spans="1:8">
       <c r="A427" t="s">
         <v>542</v>
       </c>
@@ -25403,7 +25399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="428" spans="1:8">
+    <row r="428" hidden="1" spans="1:8">
       <c r="A428" t="s">
         <v>556</v>
       </c>
@@ -25429,7 +25425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="429" spans="1:8">
+    <row r="429" hidden="1" spans="1:8">
       <c r="A429" t="s">
         <v>545</v>
       </c>
@@ -25455,7 +25451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="430" spans="1:8">
+    <row r="430" hidden="1" spans="1:8">
       <c r="A430" t="s">
         <v>539</v>
       </c>
@@ -25481,7 +25477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="431" spans="1:8">
+    <row r="431" hidden="1" spans="1:8">
       <c r="A431" t="s">
         <v>532</v>
       </c>
@@ -25507,7 +25503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="432" spans="1:8">
+    <row r="432" hidden="1" spans="1:8">
       <c r="A432" t="s">
         <v>548</v>
       </c>
@@ -25533,7 +25529,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="433" spans="1:8">
+    <row r="433" hidden="1" spans="1:8">
       <c r="A433" t="s">
         <v>554</v>
       </c>
@@ -25559,7 +25555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="434" spans="1:8">
+    <row r="434" hidden="1" spans="1:8">
       <c r="A434" t="s">
         <v>552</v>
       </c>
@@ -25585,7 +25581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="435" spans="1:8">
+    <row r="435" hidden="1" spans="1:8">
       <c r="A435" t="s">
         <v>550</v>
       </c>
@@ -25611,7 +25607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="436" spans="1:8">
+    <row r="436" hidden="1" spans="1:8">
       <c r="A436" t="s">
         <v>542</v>
       </c>
@@ -25637,7 +25633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="437" spans="1:8">
+    <row r="437" hidden="1" spans="1:8">
       <c r="A437" t="s">
         <v>556</v>
       </c>
@@ -25663,7 +25659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="438" spans="1:8">
+    <row r="438" hidden="1" spans="1:8">
       <c r="A438" t="s">
         <v>545</v>
       </c>
@@ -25689,7 +25685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="439" spans="1:8">
+    <row r="439" hidden="1" spans="1:8">
       <c r="A439" t="s">
         <v>539</v>
       </c>
@@ -25715,7 +25711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="440" spans="1:8">
+    <row r="440" hidden="1" spans="1:8">
       <c r="A440" t="s">
         <v>984</v>
       </c>
@@ -25741,7 +25737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="441" spans="1:8">
+    <row r="441" hidden="1" spans="1:8">
       <c r="A441" t="s">
         <v>984</v>
       </c>
@@ -25767,7 +25763,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="442" spans="1:8">
+    <row r="442" hidden="1" spans="1:8">
       <c r="A442" t="s">
         <v>604</v>
       </c>
@@ -25793,7 +25789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="443" spans="1:8">
+    <row r="443" hidden="1" spans="1:8">
       <c r="A443" t="s">
         <v>604</v>
       </c>
@@ -25819,7 +25815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="444" spans="1:8">
+    <row r="444" hidden="1" spans="1:8">
       <c r="A444" t="s">
         <v>604</v>
       </c>
@@ -25845,7 +25841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="445" spans="1:8">
+    <row r="445" hidden="1" spans="1:8">
       <c r="A445" t="s">
         <v>604</v>
       </c>
@@ -25871,7 +25867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="446" spans="1:8">
+    <row r="446" hidden="1" spans="1:8">
       <c r="A446" t="s">
         <v>604</v>
       </c>
@@ -25897,7 +25893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="447" spans="1:8">
+    <row r="447" hidden="1" spans="1:8">
       <c r="A447" t="s">
         <v>984</v>
       </c>
@@ -25923,7 +25919,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="448" spans="1:8">
+    <row r="448" hidden="1" spans="1:8">
       <c r="A448" t="s">
         <v>984</v>
       </c>
@@ -25949,7 +25945,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="449" spans="1:8">
+    <row r="449" hidden="1" spans="1:8">
       <c r="A449" t="s">
         <v>984</v>
       </c>
@@ -25975,7 +25971,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="450" spans="1:8">
+    <row r="450" hidden="1" spans="1:8">
       <c r="A450" t="s">
         <v>984</v>
       </c>
@@ -26001,7 +25997,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="451" spans="1:8">
+    <row r="451" hidden="1" spans="1:8">
       <c r="A451" t="s">
         <v>984</v>
       </c>
@@ -26027,7 +26023,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:8">
+    <row r="452" hidden="1" spans="1:8">
       <c r="A452" t="s">
         <v>1009</v>
       </c>
@@ -26053,7 +26049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="453" spans="1:8">
+    <row r="453" hidden="1" spans="1:8">
       <c r="A453" t="s">
         <v>741</v>
       </c>
@@ -26079,7 +26075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="454" spans="1:8">
+    <row r="454" hidden="1" spans="1:8">
       <c r="A454" t="s">
         <v>741</v>
       </c>
@@ -26105,7 +26101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="455" spans="1:8">
+    <row r="455" hidden="1" spans="1:8">
       <c r="A455" t="s">
         <v>741</v>
       </c>
@@ -26131,7 +26127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="456" spans="1:8">
+    <row r="456" hidden="1" spans="1:8">
       <c r="A456" t="s">
         <v>101</v>
       </c>
@@ -26157,7 +26153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="457" spans="1:8">
+    <row r="457" hidden="1" spans="1:8">
       <c r="A457" t="s">
         <v>101</v>
       </c>
@@ -26183,7 +26179,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="458" spans="1:8">
+    <row r="458" hidden="1" spans="1:8">
       <c r="A458" t="s">
         <v>101</v>
       </c>
@@ -26209,7 +26205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="459" spans="1:8">
+    <row r="459" hidden="1" spans="1:8">
       <c r="A459" t="s">
         <v>101</v>
       </c>
@@ -26235,7 +26231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="460" spans="1:8">
+    <row r="460" hidden="1" spans="1:8">
       <c r="A460" t="s">
         <v>101</v>
       </c>
@@ -26261,7 +26257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="461" spans="1:8">
+    <row r="461" hidden="1" spans="1:8">
       <c r="A461" t="s">
         <v>101</v>
       </c>
@@ -26287,7 +26283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="462" spans="1:8">
+    <row r="462" hidden="1" spans="1:8">
       <c r="A462" t="s">
         <v>101</v>
       </c>
@@ -26313,7 +26309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="463" spans="1:8">
+    <row r="463" hidden="1" spans="1:8">
       <c r="A463" t="s">
         <v>461</v>
       </c>
@@ -26339,7 +26335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="464" spans="1:8">
+    <row r="464" hidden="1" spans="1:8">
       <c r="A464" t="s">
         <v>461</v>
       </c>
@@ -26365,7 +26361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="465" spans="1:8">
+    <row r="465" hidden="1" spans="1:8">
       <c r="A465" t="s">
         <v>461</v>
       </c>
@@ -26391,7 +26387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="466" spans="1:8">
+    <row r="466" hidden="1" spans="1:8">
       <c r="A466" t="s">
         <v>1039</v>
       </c>
@@ -26417,7 +26413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="467" spans="1:8">
+    <row r="467" hidden="1" spans="1:8">
       <c r="A467" t="s">
         <v>461</v>
       </c>
@@ -26443,7 +26439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="468" spans="1:8">
+    <row r="468" hidden="1" spans="1:8">
       <c r="A468" t="s">
         <v>461</v>
       </c>
@@ -26469,7 +26465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="469" spans="1:8">
+    <row r="469" hidden="1" spans="1:8">
       <c r="A469" t="s">
         <v>461</v>
       </c>
@@ -26495,7 +26491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="470" spans="1:8">
+    <row r="470" hidden="1" spans="1:8">
       <c r="A470" t="s">
         <v>1039</v>
       </c>
@@ -26521,7 +26517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:8">
+    <row r="471" hidden="1" spans="1:8">
       <c r="A471" t="s">
         <v>461</v>
       </c>
@@ -26547,7 +26543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="472" spans="1:8">
+    <row r="472" hidden="1" spans="1:8">
       <c r="A472" t="s">
         <v>461</v>
       </c>
@@ -26573,7 +26569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="473" spans="1:8">
+    <row r="473" hidden="1" spans="1:8">
       <c r="A473" t="s">
         <v>461</v>
       </c>
@@ -26599,7 +26595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" spans="1:8">
+    <row r="474" hidden="1" spans="1:8">
       <c r="A474" t="s">
         <v>461</v>
       </c>
@@ -26625,7 +26621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="475" spans="1:8">
+    <row r="475" hidden="1" spans="1:8">
       <c r="A475" t="s">
         <v>461</v>
       </c>
@@ -26651,7 +26647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="476" spans="1:8">
+    <row r="476" hidden="1" spans="1:8">
       <c r="A476" t="s">
         <v>461</v>
       </c>
@@ -26677,7 +26673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="477" spans="1:8">
+    <row r="477" hidden="1" spans="1:8">
       <c r="A477" t="s">
         <v>816</v>
       </c>
@@ -26703,7 +26699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="478" spans="1:8">
+    <row r="478" hidden="1" spans="1:8">
       <c r="A478" t="s">
         <v>816</v>
       </c>
@@ -26729,7 +26725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="479" spans="1:8">
+    <row r="479" hidden="1" spans="1:8">
       <c r="A479" t="s">
         <v>816</v>
       </c>
@@ -26755,7 +26751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="480" spans="1:8">
+    <row r="480" hidden="1" spans="1:8">
       <c r="A480" t="s">
         <v>816</v>
       </c>
@@ -26781,7 +26777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="481" spans="1:8">
+    <row r="481" hidden="1" spans="1:8">
       <c r="A481" t="s">
         <v>461</v>
       </c>
@@ -26807,7 +26803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="482" spans="1:8">
+    <row r="482" hidden="1" spans="1:8">
       <c r="A482" t="s">
         <v>461</v>
       </c>
@@ -26833,7 +26829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="483" spans="1:8">
+    <row r="483" hidden="1" spans="1:8">
       <c r="A483" t="s">
         <v>461</v>
       </c>
@@ -26859,7 +26855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="484" spans="1:8">
+    <row r="484" hidden="1" spans="1:8">
       <c r="A484" t="s">
         <v>461</v>
       </c>
@@ -26885,7 +26881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="485" spans="1:8">
+    <row r="485" hidden="1" spans="1:8">
       <c r="A485" t="s">
         <v>461</v>
       </c>
@@ -26911,7 +26907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="486" spans="1:8">
+    <row r="486" hidden="1" spans="1:8">
       <c r="A486" t="s">
         <v>461</v>
       </c>
@@ -26937,7 +26933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="487" spans="1:8">
+    <row r="487" hidden="1" spans="1:8">
       <c r="A487" t="s">
         <v>461</v>
       </c>
@@ -26963,7 +26959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="488" spans="1:8">
+    <row r="488" hidden="1" spans="1:8">
       <c r="A488" t="s">
         <v>461</v>
       </c>
@@ -26989,7 +26985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" spans="1:8">
+    <row r="489" hidden="1" spans="1:8">
       <c r="A489" t="s">
         <v>461</v>
       </c>
@@ -27015,7 +27011,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="490" spans="1:8">
+    <row r="490" hidden="1" spans="1:8">
       <c r="A490" t="s">
         <v>461</v>
       </c>
@@ -27041,7 +27037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="491" spans="1:8">
+    <row r="491" hidden="1" spans="1:8">
       <c r="A491" t="s">
         <v>461</v>
       </c>
@@ -27067,7 +27063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="492" spans="1:8">
+    <row r="492" hidden="1" spans="1:8">
       <c r="A492" t="s">
         <v>1094</v>
       </c>
@@ -27093,7 +27089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="493" spans="1:8">
+    <row r="493" hidden="1" spans="1:8">
       <c r="A493" t="s">
         <v>1094</v>
       </c>
@@ -27119,7 +27115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="494" spans="1:8">
+    <row r="494" hidden="1" spans="1:8">
       <c r="A494" t="s">
         <v>1094</v>
       </c>
@@ -27145,7 +27141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="495" spans="1:8">
+    <row r="495" hidden="1" spans="1:8">
       <c r="A495" t="s">
         <v>1094</v>
       </c>
@@ -27171,7 +27167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="496" spans="1:8">
+    <row r="496" hidden="1" spans="1:8">
       <c r="A496" t="s">
         <v>1094</v>
       </c>
@@ -27197,7 +27193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" hidden="1" spans="1:8">
       <c r="A497" t="s">
         <v>1094</v>
       </c>
@@ -27223,7 +27219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" hidden="1" spans="1:8">
       <c r="A498" t="s">
         <v>1094</v>
       </c>
@@ -27249,7 +27245,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" hidden="1" spans="1:8">
       <c r="A499" t="s">
         <v>1094</v>
       </c>
@@ -27275,7 +27271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" hidden="1" spans="1:8">
       <c r="A500" t="s">
         <v>1111</v>
       </c>
@@ -27301,7 +27297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" hidden="1" spans="1:8">
       <c r="A501" t="s">
         <v>1111</v>
       </c>
@@ -27327,7 +27323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="502" spans="1:8">
+    <row r="502" hidden="1" spans="1:8">
       <c r="A502" t="s">
         <v>1111</v>
       </c>
@@ -27353,7 +27349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" hidden="1" spans="1:8">
       <c r="A503" t="s">
         <v>1111</v>
       </c>
@@ -27379,7 +27375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" hidden="1" spans="1:8">
       <c r="A504" t="s">
         <v>1111</v>
       </c>
@@ -27405,7 +27401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" hidden="1" spans="1:8">
       <c r="A505" t="s">
         <v>1111</v>
       </c>
@@ -27431,7 +27427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" hidden="1" spans="1:8">
       <c r="A506" t="s">
         <v>1111</v>
       </c>
@@ -27457,7 +27453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" hidden="1" spans="1:8">
       <c r="A507" t="s">
         <v>282</v>
       </c>
@@ -27483,7 +27479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" hidden="1" spans="1:8">
       <c r="A508" t="s">
         <v>1111</v>
       </c>
@@ -27509,7 +27505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" hidden="1" spans="1:8">
       <c r="A509" t="s">
         <v>1123</v>
       </c>
@@ -27535,7 +27531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" hidden="1" spans="1:8">
       <c r="A510" t="s">
         <v>1123</v>
       </c>
@@ -27561,7 +27557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" hidden="1" spans="1:8">
       <c r="A511" t="s">
         <v>1123</v>
       </c>
@@ -27587,7 +27583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="512" spans="1:8">
+    <row r="512" hidden="1" spans="1:8">
       <c r="A512" t="s">
         <v>1123</v>
       </c>
@@ -27613,7 +27609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="513" spans="1:8">
+    <row r="513" hidden="1" spans="1:8">
       <c r="A513" t="s">
         <v>1123</v>
       </c>
@@ -27639,7 +27635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="514" spans="1:8">
+    <row r="514" hidden="1" spans="1:8">
       <c r="A514" t="s">
         <v>1130</v>
       </c>
@@ -27665,7 +27661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="515" spans="1:8">
+    <row r="515" hidden="1" spans="1:8">
       <c r="A515" t="s">
         <v>1130</v>
       </c>
@@ -27691,7 +27687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="516" spans="1:8">
+    <row r="516" hidden="1" spans="1:8">
       <c r="A516" t="s">
         <v>1130</v>
       </c>
@@ -27717,7 +27713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="517" spans="1:8">
+    <row r="517" hidden="1" spans="1:8">
       <c r="A517" t="s">
         <v>1130</v>
       </c>
@@ -27743,7 +27739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="518" spans="1:8">
+    <row r="518" hidden="1" spans="1:8">
       <c r="A518" t="s">
         <v>1130</v>
       </c>
@@ -27769,7 +27765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="519" spans="1:8">
+    <row r="519" hidden="1" spans="1:8">
       <c r="A519" t="s">
         <v>405</v>
       </c>
@@ -27795,7 +27791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="520" spans="1:8">
+    <row r="520" hidden="1" spans="1:8">
       <c r="A520" t="s">
         <v>1145</v>
       </c>
@@ -27821,7 +27817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="521" spans="1:8">
+    <row r="521" hidden="1" spans="1:8">
       <c r="A521" t="s">
         <v>1145</v>
       </c>
@@ -27847,7 +27843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="522" spans="1:8">
+    <row r="522" hidden="1" spans="1:8">
       <c r="A522" t="s">
         <v>1145</v>
       </c>
@@ -27873,7 +27869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="523" spans="1:8">
+    <row r="523" hidden="1" spans="1:8">
       <c r="A523" t="s">
         <v>1145</v>
       </c>
@@ -27899,7 +27895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="524" spans="1:8">
+    <row r="524" hidden="1" spans="1:8">
       <c r="A524" t="s">
         <v>1145</v>
       </c>
@@ -27925,7 +27921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="525" spans="1:8">
+    <row r="525" hidden="1" spans="1:8">
       <c r="A525" t="s">
         <v>1145</v>
       </c>
@@ -27951,7 +27947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="526" spans="1:8">
+    <row r="526" hidden="1" spans="1:8">
       <c r="A526" t="s">
         <v>1145</v>
       </c>
@@ -27977,7 +27973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="527" spans="1:8">
+    <row r="527" hidden="1" spans="1:8">
       <c r="A527" t="s">
         <v>1145</v>
       </c>
@@ -28003,7 +27999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="528" spans="1:8">
+    <row r="528" hidden="1" spans="1:8">
       <c r="A528" t="s">
         <v>1145</v>
       </c>
@@ -28029,7 +28025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="529" spans="1:8">
+    <row r="529" hidden="1" spans="1:8">
       <c r="A529" t="s">
         <v>468</v>
       </c>
@@ -28055,7 +28051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="530" spans="1:8">
+    <row r="530" hidden="1" spans="1:8">
       <c r="A530" t="s">
         <v>468</v>
       </c>
@@ -28081,7 +28077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="531" spans="1:8">
+    <row r="531" hidden="1" spans="1:8">
       <c r="A531" t="s">
         <v>468</v>
       </c>
@@ -28107,7 +28103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="532" spans="1:8">
+    <row r="532" hidden="1" spans="1:8">
       <c r="A532" t="s">
         <v>468</v>
       </c>
@@ -28133,7 +28129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="533" spans="1:8">
+    <row r="533" hidden="1" spans="1:8">
       <c r="A533" t="s">
         <v>468</v>
       </c>
@@ -28159,7 +28155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="534" spans="1:8">
+    <row r="534" hidden="1" spans="1:8">
       <c r="A534" t="s">
         <v>468</v>
       </c>
@@ -28185,7 +28181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="535" spans="1:8">
+    <row r="535" hidden="1" spans="1:8">
       <c r="A535" t="s">
         <v>468</v>
       </c>
@@ -28211,7 +28207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" hidden="1" spans="1:8">
       <c r="A536" t="s">
         <v>468</v>
       </c>
@@ -28237,7 +28233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="537" spans="1:8">
+    <row r="537" hidden="1" spans="1:8">
       <c r="A537" t="s">
         <v>468</v>
       </c>
@@ -28263,7 +28259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="538" spans="1:8">
+    <row r="538" hidden="1" spans="1:8">
       <c r="A538" t="s">
         <v>57</v>
       </c>
@@ -28289,7 +28285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="539" spans="1:8">
+    <row r="539" hidden="1" spans="1:8">
       <c r="A539" t="s">
         <v>57</v>
       </c>
@@ -28315,7 +28311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="540" spans="1:8">
+    <row r="540" hidden="1" spans="1:8">
       <c r="A540" t="s">
         <v>57</v>
       </c>
@@ -28341,7 +28337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="541" spans="1:8">
+    <row r="541" hidden="1" spans="1:8">
       <c r="A541" t="s">
         <v>57</v>
       </c>
@@ -28367,7 +28363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="542" spans="1:8">
+    <row r="542" hidden="1" spans="1:8">
       <c r="A542" t="s">
         <v>1189</v>
       </c>
@@ -28393,7 +28389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="543" spans="1:8">
+    <row r="543" hidden="1" spans="1:8">
       <c r="A543" t="s">
         <v>1194</v>
       </c>
@@ -28419,7 +28415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="544" spans="1:8">
+    <row r="544" hidden="1" spans="1:8">
       <c r="A544" t="s">
         <v>1197</v>
       </c>
@@ -28445,7 +28441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="545" spans="1:8">
+    <row r="545" hidden="1" spans="1:8">
       <c r="A545" t="s">
         <v>1189</v>
       </c>
@@ -28471,7 +28467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="546" spans="1:8">
+    <row r="546" hidden="1" spans="1:8">
       <c r="A546" t="s">
         <v>1194</v>
       </c>
@@ -28497,7 +28493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="547" spans="1:8">
+    <row r="547" hidden="1" spans="1:8">
       <c r="A547" t="s">
         <v>1197</v>
       </c>
@@ -28523,7 +28519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="548" spans="1:8">
+    <row r="548" hidden="1" spans="1:8">
       <c r="A548" t="s">
         <v>1189</v>
       </c>
@@ -28549,7 +28545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="549" spans="1:8">
+    <row r="549" hidden="1" spans="1:8">
       <c r="A549" t="s">
         <v>1194</v>
       </c>
@@ -28575,7 +28571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="550" spans="1:8">
+    <row r="550" hidden="1" spans="1:8">
       <c r="A550" t="s">
         <v>1197</v>
       </c>
@@ -28601,7 +28597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="551" spans="1:8">
+    <row r="551" hidden="1" spans="1:8">
       <c r="A551" t="s">
         <v>1189</v>
       </c>
@@ -28627,7 +28623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="552" spans="1:8">
+    <row r="552" hidden="1" spans="1:8">
       <c r="A552" t="s">
         <v>1194</v>
       </c>
@@ -28653,7 +28649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="553" spans="1:8">
+    <row r="553" hidden="1" spans="1:8">
       <c r="A553" t="s">
         <v>1197</v>
       </c>
@@ -28679,7 +28675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="554" spans="1:8">
+    <row r="554" hidden="1" spans="1:8">
       <c r="A554" t="s">
         <v>629</v>
       </c>
@@ -28705,7 +28701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="555" spans="1:8">
+    <row r="555" hidden="1" spans="1:8">
       <c r="A555" t="s">
         <v>629</v>
       </c>
@@ -28731,7 +28727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" spans="1:8">
+    <row r="556" hidden="1" spans="1:8">
       <c r="A556" t="s">
         <v>622</v>
       </c>
@@ -28757,7 +28753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="557" spans="1:8">
+    <row r="557" hidden="1" spans="1:8">
       <c r="A557" t="s">
         <v>629</v>
       </c>
@@ -28783,7 +28779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" hidden="1" spans="1:8">
       <c r="A558" t="s">
         <v>629</v>
       </c>
@@ -28809,7 +28805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="559" spans="1:8">
+    <row r="559" hidden="1" spans="1:8">
       <c r="A559" t="s">
         <v>622</v>
       </c>
@@ -28835,7 +28831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="560" spans="1:8">
+    <row r="560" hidden="1" spans="1:8">
       <c r="A560" t="s">
         <v>629</v>
       </c>
@@ -28861,7 +28857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="561" spans="1:8">
+    <row r="561" hidden="1" spans="1:8">
       <c r="A561" t="s">
         <v>622</v>
       </c>
@@ -28887,7 +28883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="562" spans="1:8">
+    <row r="562" hidden="1" spans="1:8">
       <c r="A562" t="s">
         <v>629</v>
       </c>
@@ -28913,7 +28909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="563" spans="1:8">
+    <row r="563" hidden="1" spans="1:8">
       <c r="A563" t="s">
         <v>461</v>
       </c>
@@ -28939,7 +28935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="564" spans="1:8">
+    <row r="564" hidden="1" spans="1:8">
       <c r="A564" t="s">
         <v>461</v>
       </c>
@@ -28965,7 +28961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="565" spans="1:8">
+    <row r="565" hidden="1" spans="1:8">
       <c r="A565" t="s">
         <v>461</v>
       </c>
@@ -28991,7 +28987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="566" spans="1:8">
+    <row r="566" hidden="1" spans="1:8">
       <c r="A566" t="s">
         <v>461</v>
       </c>
@@ -29017,7 +29013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="567" spans="1:8">
+    <row r="567" hidden="1" spans="1:8">
       <c r="A567" t="s">
         <v>461</v>
       </c>
@@ -29043,7 +29039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="568" spans="1:8">
+    <row r="568" hidden="1" spans="1:8">
       <c r="A568" t="s">
         <v>461</v>
       </c>
@@ -29069,7 +29065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="569" spans="1:8">
+    <row r="569" hidden="1" spans="1:8">
       <c r="A569" t="s">
         <v>461</v>
       </c>
@@ -29095,7 +29091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="570" spans="1:8">
+    <row r="570" hidden="1" spans="1:8">
       <c r="A570" t="s">
         <v>461</v>
       </c>
@@ -29121,7 +29117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="571" spans="1:8">
+    <row r="571" hidden="1" spans="1:8">
       <c r="A571" t="s">
         <v>461</v>
       </c>
@@ -29147,7 +29143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="572" spans="1:8">
+    <row r="572" hidden="1" spans="1:8">
       <c r="A572" t="s">
         <v>461</v>
       </c>
@@ -29173,7 +29169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="573" spans="1:8">
+    <row r="573" hidden="1" spans="1:8">
       <c r="A573" t="s">
         <v>461</v>
       </c>
@@ -29199,7 +29195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="574" spans="1:8">
+    <row r="574" hidden="1" spans="1:8">
       <c r="A574" t="s">
         <v>461</v>
       </c>
@@ -29225,7 +29221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="575" spans="1:8">
+    <row r="575" hidden="1" spans="1:8">
       <c r="A575" t="s">
         <v>18</v>
       </c>
@@ -29251,7 +29247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="576" spans="1:8">
+    <row r="576" hidden="1" spans="1:8">
       <c r="A576" t="s">
         <v>1247</v>
       </c>
@@ -29277,7 +29273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="577" spans="1:8">
+    <row r="577" hidden="1" spans="1:8">
       <c r="A577" t="s">
         <v>1247</v>
       </c>
@@ -29303,7 +29299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="578" spans="1:8">
+    <row r="578" hidden="1" spans="1:8">
       <c r="A578" t="s">
         <v>1247</v>
       </c>
@@ -29329,7 +29325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="579" spans="1:8">
+    <row r="579" hidden="1" spans="1:8">
       <c r="A579" t="s">
         <v>1247</v>
       </c>
@@ -29355,7 +29351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="580" spans="1:8">
+    <row r="580" hidden="1" spans="1:8">
       <c r="A580" t="s">
         <v>1247</v>
       </c>
@@ -29381,7 +29377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="581" spans="1:8">
+    <row r="581" hidden="1" spans="1:8">
       <c r="A581" t="s">
         <v>252</v>
       </c>
@@ -29407,7 +29403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="582" spans="1:8">
+    <row r="582" hidden="1" spans="1:8">
       <c r="A582" t="s">
         <v>252</v>
       </c>
@@ -29433,7 +29429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="583" spans="1:8">
+    <row r="583" hidden="1" spans="1:8">
       <c r="A583" t="s">
         <v>252</v>
       </c>
@@ -29459,7 +29455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="584" spans="1:8">
+    <row r="584" hidden="1" spans="1:8">
       <c r="A584" t="s">
         <v>252</v>
       </c>
@@ -29485,7 +29481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="585" spans="1:8">
+    <row r="585" hidden="1" spans="1:8">
       <c r="A585" t="s">
         <v>252</v>
       </c>
@@ -29511,7 +29507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="586" spans="1:8">
+    <row r="586" hidden="1" spans="1:8">
       <c r="A586" t="s">
         <v>252</v>
       </c>
@@ -29537,7 +29533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="587" spans="1:8">
+    <row r="587" hidden="1" spans="1:8">
       <c r="A587" t="s">
         <v>252</v>
       </c>
@@ -29563,7 +29559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="588" spans="1:8">
+    <row r="588" hidden="1" spans="1:8">
       <c r="A588" t="s">
         <v>712</v>
       </c>
@@ -29589,7 +29585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="589" spans="1:8">
+    <row r="589" hidden="1" spans="1:8">
       <c r="A589" t="s">
         <v>712</v>
       </c>
@@ -29615,7 +29611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="590" spans="1:8">
+    <row r="590" hidden="1" spans="1:8">
       <c r="A590" t="s">
         <v>712</v>
       </c>
@@ -29641,7 +29637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="591" spans="1:8">
+    <row r="591" hidden="1" spans="1:8">
       <c r="A591" t="s">
         <v>712</v>
       </c>
@@ -29667,7 +29663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="592" spans="1:8">
+    <row r="592" hidden="1" spans="1:8">
       <c r="A592" t="s">
         <v>712</v>
       </c>
@@ -29693,7 +29689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="593" spans="1:8">
+    <row r="593" hidden="1" spans="1:8">
       <c r="A593" t="s">
         <v>53</v>
       </c>
@@ -29719,7 +29715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="594" spans="1:8">
+    <row r="594" hidden="1" spans="1:8">
       <c r="A594" t="s">
         <v>53</v>
       </c>
@@ -29745,7 +29741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="595" spans="1:8">
+    <row r="595" hidden="1" spans="1:8">
       <c r="A595" t="s">
         <v>53</v>
       </c>
@@ -29771,7 +29767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="596" spans="1:8">
+    <row r="596" hidden="1" spans="1:8">
       <c r="A596" t="s">
         <v>53</v>
       </c>
@@ -29797,7 +29793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="597" spans="1:8">
+    <row r="597" hidden="1" spans="1:8">
       <c r="A597" t="s">
         <v>736</v>
       </c>
@@ -29823,7 +29819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="598" spans="1:8">
+    <row r="598" hidden="1" spans="1:8">
       <c r="A598" t="s">
         <v>736</v>
       </c>
@@ -29849,7 +29845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="599" spans="1:8">
+    <row r="599" hidden="1" spans="1:8">
       <c r="A599" t="s">
         <v>736</v>
       </c>
@@ -29875,7 +29871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="600" spans="1:8">
+    <row r="600" hidden="1" spans="1:8">
       <c r="A600" t="s">
         <v>1295</v>
       </c>
@@ -29901,7 +29897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="601" spans="1:8">
+    <row r="601" hidden="1" spans="1:8">
       <c r="A601" t="s">
         <v>259</v>
       </c>
@@ -29927,7 +29923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="602" spans="1:8">
+    <row r="602" hidden="1" spans="1:8">
       <c r="A602" t="s">
         <v>259</v>
       </c>
@@ -29953,7 +29949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="603" spans="1:8">
+    <row r="603" hidden="1" spans="1:8">
       <c r="A603" t="s">
         <v>259</v>
       </c>
@@ -29979,7 +29975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="604" spans="1:8">
+    <row r="604" hidden="1" spans="1:8">
       <c r="A604" t="s">
         <v>259</v>
       </c>
@@ -30005,7 +30001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="605" spans="1:8">
+    <row r="605" hidden="1" spans="1:8">
       <c r="A605" t="s">
         <v>259</v>
       </c>
@@ -30031,7 +30027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="606" spans="1:8">
+    <row r="606" hidden="1" spans="1:8">
       <c r="A606" t="s">
         <v>259</v>
       </c>
@@ -30057,7 +30053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="607" spans="1:8">
+    <row r="607" hidden="1" spans="1:8">
       <c r="A607" t="s">
         <v>259</v>
       </c>
@@ -30083,7 +30079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="608" spans="1:8">
+    <row r="608" hidden="1" spans="1:8">
       <c r="A608" t="s">
         <v>259</v>
       </c>
@@ -30109,7 +30105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="609" spans="1:8">
+    <row r="609" hidden="1" spans="1:8">
       <c r="A609" t="s">
         <v>259</v>
       </c>
@@ -30135,7 +30131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="610" spans="1:8">
+    <row r="610" hidden="1" spans="1:8">
       <c r="A610" t="s">
         <v>259</v>
       </c>
@@ -30161,7 +30157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="611" spans="1:8">
+    <row r="611" hidden="1" spans="1:8">
       <c r="A611" t="s">
         <v>259</v>
       </c>
@@ -30187,7 +30183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="612" spans="1:8">
+    <row r="612" hidden="1" spans="1:8">
       <c r="A612" t="s">
         <v>259</v>
       </c>
@@ -30213,7 +30209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="613" spans="1:8">
+    <row r="613" hidden="1" spans="1:8">
       <c r="A613" t="s">
         <v>259</v>
       </c>
@@ -30291,7 +30287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="616" spans="1:8">
+    <row r="616" hidden="1" spans="1:8">
       <c r="A616" t="s">
         <v>111</v>
       </c>
@@ -30369,7 +30365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="619" spans="1:8">
+    <row r="619" hidden="1" spans="1:8">
       <c r="A619" t="s">
         <v>111</v>
       </c>
@@ -30499,7 +30495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="624" spans="1:8">
+    <row r="624" hidden="1" spans="1:8">
       <c r="A624" t="s">
         <v>111</v>
       </c>
@@ -30629,7 +30625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="629" spans="1:8">
+    <row r="629" hidden="1" spans="1:8">
       <c r="A629" t="s">
         <v>1039</v>
       </c>
@@ -30655,7 +30651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="630" spans="1:8">
+    <row r="630" hidden="1" spans="1:8">
       <c r="A630" t="s">
         <v>461</v>
       </c>
@@ -30681,7 +30677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="631" spans="1:8">
+    <row r="631" hidden="1" spans="1:8">
       <c r="A631" t="s">
         <v>612</v>
       </c>
@@ -30707,7 +30703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="632" spans="1:8">
+    <row r="632" hidden="1" spans="1:8">
       <c r="A632" t="s">
         <v>612</v>
       </c>
@@ -30733,7 +30729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="633" spans="1:8">
+    <row r="633" hidden="1" spans="1:8">
       <c r="A633" t="s">
         <v>612</v>
       </c>
@@ -30759,7 +30755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="634" spans="1:8">
+    <row r="634" hidden="1" spans="1:8">
       <c r="A634" t="s">
         <v>612</v>
       </c>
@@ -30785,7 +30781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="635" spans="1:8">
+    <row r="635" hidden="1" spans="1:8">
       <c r="A635" t="s">
         <v>612</v>
       </c>
@@ -30811,7 +30807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="636" spans="1:8">
+    <row r="636" hidden="1" spans="1:8">
       <c r="A636" t="s">
         <v>612</v>
       </c>
@@ -30837,7 +30833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="637" spans="1:8">
+    <row r="637" hidden="1" spans="1:8">
       <c r="A637" t="s">
         <v>441</v>
       </c>
@@ -30863,7 +30859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="638" spans="1:8">
+    <row r="638" hidden="1" spans="1:8">
       <c r="A638" t="s">
         <v>436</v>
       </c>
@@ -30889,7 +30885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="639" spans="1:8">
+    <row r="639" hidden="1" spans="1:8">
       <c r="A639" t="s">
         <v>441</v>
       </c>
@@ -30915,7 +30911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="640" spans="1:8">
+    <row r="640" hidden="1" spans="1:8">
       <c r="A640" t="s">
         <v>436</v>
       </c>
@@ -30941,7 +30937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="641" spans="1:8">
+    <row r="641" hidden="1" spans="1:8">
       <c r="A641" t="s">
         <v>1352</v>
       </c>
@@ -30967,7 +30963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="642" spans="1:8">
+    <row r="642" hidden="1" spans="1:8">
       <c r="A642" t="s">
         <v>1352</v>
       </c>
@@ -30993,7 +30989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="643" spans="1:8">
+    <row r="643" hidden="1" spans="1:8">
       <c r="A643" t="s">
         <v>1352</v>
       </c>
@@ -31019,7 +31015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="644" spans="1:8">
+    <row r="644" hidden="1" spans="1:8">
       <c r="A644" t="s">
         <v>1352</v>
       </c>
@@ -31045,7 +31041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="645" spans="1:8">
+    <row r="645" hidden="1" spans="1:8">
       <c r="A645" t="s">
         <v>1352</v>
       </c>
@@ -31071,7 +31067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="646" spans="1:8">
+    <row r="646" hidden="1" spans="1:8">
       <c r="A646" t="s">
         <v>1352</v>
       </c>
@@ -31097,7 +31093,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="647" spans="1:8">
+    <row r="647" hidden="1" spans="1:8">
       <c r="A647" t="s">
         <v>1352</v>
       </c>
@@ -31123,7 +31119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="648" spans="1:8">
+    <row r="648" hidden="1" spans="1:8">
       <c r="A648" t="s">
         <v>1352</v>
       </c>
@@ -31149,7 +31145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="649" spans="1:8">
+    <row r="649" hidden="1" spans="1:8">
       <c r="A649" t="s">
         <v>1352</v>
       </c>
@@ -31175,7 +31171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="650" spans="1:8">
+    <row r="650" hidden="1" spans="1:8">
       <c r="A650" t="s">
         <v>243</v>
       </c>
@@ -31201,7 +31197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="651" spans="1:8">
+    <row r="651" hidden="1" spans="1:8">
       <c r="A651" t="s">
         <v>243</v>
       </c>
@@ -31227,7 +31223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="652" spans="1:8">
+    <row r="652" hidden="1" spans="1:8">
       <c r="A652" t="s">
         <v>243</v>
       </c>
@@ -31253,7 +31249,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="653" spans="1:8">
+    <row r="653" hidden="1" spans="1:8">
       <c r="A653" t="s">
         <v>243</v>
       </c>
@@ -31279,7 +31275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="654" spans="1:8">
+    <row r="654" hidden="1" spans="1:8">
       <c r="A654" t="s">
         <v>243</v>
       </c>
@@ -31305,7 +31301,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="655" spans="1:8">
+    <row r="655" hidden="1" spans="1:8">
       <c r="A655" t="s">
         <v>243</v>
       </c>
@@ -31331,7 +31327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="656" spans="1:8">
+    <row r="656" hidden="1" spans="1:8">
       <c r="A656" t="s">
         <v>243</v>
       </c>
@@ -31357,7 +31353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="657" spans="1:8">
+    <row r="657" hidden="1" spans="1:8">
       <c r="A657" t="s">
         <v>243</v>
       </c>
@@ -31383,7 +31379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="658" spans="1:8">
+    <row r="658" hidden="1" spans="1:8">
       <c r="A658" t="s">
         <v>243</v>
       </c>
@@ -31409,7 +31405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="659" spans="1:8">
+    <row r="659" hidden="1" spans="1:8">
       <c r="A659" t="s">
         <v>243</v>
       </c>
@@ -31435,7 +31431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="660" spans="1:8">
+    <row r="660" hidden="1" spans="1:8">
       <c r="A660" t="s">
         <v>243</v>
       </c>
@@ -31461,7 +31457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="661" spans="1:8">
+    <row r="661" hidden="1" spans="1:8">
       <c r="A661" t="s">
         <v>1393</v>
       </c>
@@ -31487,7 +31483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="662" spans="1:8">
+    <row r="662" hidden="1" spans="1:8">
       <c r="A662" t="s">
         <v>1393</v>
       </c>
@@ -31513,7 +31509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="663" spans="1:8">
+    <row r="663" hidden="1" spans="1:8">
       <c r="A663" t="s">
         <v>1393</v>
       </c>
@@ -31539,7 +31535,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="664" spans="1:8">
+    <row r="664" hidden="1" spans="1:8">
       <c r="A664" t="s">
         <v>1393</v>
       </c>
@@ -31565,7 +31561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="665" spans="1:8">
+    <row r="665" hidden="1" spans="1:8">
       <c r="A665" t="s">
         <v>1393</v>
       </c>
@@ -31591,7 +31587,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="666" spans="1:8">
+    <row r="666" hidden="1" spans="1:8">
       <c r="A666" t="s">
         <v>1393</v>
       </c>
@@ -31617,7 +31613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="667" spans="1:8">
+    <row r="667" hidden="1" spans="1:8">
       <c r="A667" t="s">
         <v>1393</v>
       </c>
@@ -31643,7 +31639,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="668" spans="1:8">
+    <row r="668" hidden="1" spans="1:8">
       <c r="A668" t="s">
         <v>1393</v>
       </c>
@@ -31669,7 +31665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="669" spans="1:8">
+    <row r="669" hidden="1" spans="1:8">
       <c r="A669" t="s">
         <v>1393</v>
       </c>
@@ -31695,7 +31691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="670" spans="1:8">
+    <row r="670" hidden="1" spans="1:8">
       <c r="A670" t="s">
         <v>1393</v>
       </c>
@@ -31721,7 +31717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="671" spans="1:8">
+    <row r="671" hidden="1" spans="1:8">
       <c r="A671" t="s">
         <v>1393</v>
       </c>
@@ -31747,7 +31743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="672" spans="1:8">
+    <row r="672" hidden="1" spans="1:8">
       <c r="A672" t="s">
         <v>1393</v>
       </c>
@@ -31773,7 +31769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="673" spans="1:8">
+    <row r="673" hidden="1" spans="1:8">
       <c r="A673" t="s">
         <v>1393</v>
       </c>
@@ -31799,7 +31795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="674" spans="1:8">
+    <row r="674" hidden="1" spans="1:8">
       <c r="A674" t="s">
         <v>1419</v>
       </c>
@@ -31825,7 +31821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="675" spans="1:8">
+    <row r="675" hidden="1" spans="1:8">
       <c r="A675" t="s">
         <v>243</v>
       </c>
@@ -31851,7 +31847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="676" spans="1:8">
+    <row r="676" hidden="1" spans="1:8">
       <c r="A676" t="s">
         <v>243</v>
       </c>
@@ -31877,7 +31873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="677" spans="1:8">
+    <row r="677" hidden="1" spans="1:8">
       <c r="A677" t="s">
         <v>243</v>
       </c>
@@ -31903,7 +31899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="678" spans="1:8">
+    <row r="678" hidden="1" spans="1:8">
       <c r="A678" t="s">
         <v>243</v>
       </c>
@@ -31929,7 +31925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="679" spans="1:8">
+    <row r="679" hidden="1" spans="1:8">
       <c r="A679" t="s">
         <v>243</v>
       </c>
@@ -31955,7 +31951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="680" spans="1:8">
+    <row r="680" hidden="1" spans="1:8">
       <c r="A680" t="s">
         <v>243</v>
       </c>
@@ -31981,7 +31977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="681" spans="1:8">
+    <row r="681" hidden="1" spans="1:8">
       <c r="A681" t="s">
         <v>243</v>
       </c>
@@ -32007,7 +32003,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="682" spans="1:8">
+    <row r="682" hidden="1" spans="1:8">
       <c r="A682" t="s">
         <v>243</v>
       </c>
@@ -32033,7 +32029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="683" spans="1:8">
+    <row r="683" hidden="1" spans="1:8">
       <c r="A683" t="s">
         <v>243</v>
       </c>
@@ -32059,7 +32055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="684" spans="1:8">
+    <row r="684" hidden="1" spans="1:8">
       <c r="A684" t="s">
         <v>243</v>
       </c>
@@ -32085,7 +32081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="685" spans="1:8">
+    <row r="685" hidden="1" spans="1:8">
       <c r="A685" t="s">
         <v>243</v>
       </c>
@@ -32111,7 +32107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="686" spans="1:8">
+    <row r="686" hidden="1" spans="1:8">
       <c r="A686" t="s">
         <v>243</v>
       </c>
@@ -32137,7 +32133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="687" spans="1:8">
+    <row r="687" hidden="1" spans="1:8">
       <c r="A687" t="s">
         <v>243</v>
       </c>
@@ -32163,7 +32159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="688" spans="1:8">
+    <row r="688" hidden="1" spans="1:8">
       <c r="A688" t="s">
         <v>243</v>
       </c>
@@ -32189,7 +32185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="689" spans="1:8">
+    <row r="689" hidden="1" spans="1:8">
       <c r="A689" t="s">
         <v>243</v>
       </c>
@@ -32215,7 +32211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="690" spans="1:8">
+    <row r="690" hidden="1" spans="1:8">
       <c r="A690" t="s">
         <v>243</v>
       </c>
@@ -32241,7 +32237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="691" spans="1:8">
+    <row r="691" hidden="1" spans="1:8">
       <c r="A691" t="s">
         <v>1455</v>
       </c>
@@ -32267,7 +32263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="692" spans="1:8">
+    <row r="692" hidden="1" spans="1:8">
       <c r="A692" t="s">
         <v>160</v>
       </c>
@@ -32293,7 +32289,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="693" spans="1:8">
+    <row r="693" hidden="1" spans="1:8">
       <c r="A693" t="s">
         <v>153</v>
       </c>
@@ -32319,7 +32315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="694" spans="1:8">
+    <row r="694" hidden="1" spans="1:8">
       <c r="A694" t="s">
         <v>1463</v>
       </c>
@@ -32345,7 +32341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="695" spans="1:8">
+    <row r="695" hidden="1" spans="1:8">
       <c r="A695" t="s">
         <v>160</v>
       </c>
@@ -32371,7 +32367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="696" spans="1:8">
+    <row r="696" hidden="1" spans="1:8">
       <c r="A696" t="s">
         <v>156</v>
       </c>
@@ -32397,7 +32393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="697" spans="1:8">
+    <row r="697" hidden="1" spans="1:8">
       <c r="A697" t="s">
         <v>1468</v>
       </c>
@@ -32423,7 +32419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="698" spans="1:8">
+    <row r="698" hidden="1" spans="1:8">
       <c r="A698" t="s">
         <v>1472</v>
       </c>
@@ -32449,7 +32445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="699" spans="1:8">
+    <row r="699" hidden="1" spans="1:8">
       <c r="A699" t="s">
         <v>1475</v>
       </c>
@@ -32475,7 +32471,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="700" spans="1:8">
+    <row r="700" hidden="1" spans="1:8">
       <c r="A700" t="s">
         <v>1479</v>
       </c>
@@ -32501,7 +32497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="701" spans="1:8">
+    <row r="701" hidden="1" spans="1:8">
       <c r="A701" t="s">
         <v>1472</v>
       </c>
@@ -32527,7 +32523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="702" spans="1:8">
+    <row r="702" hidden="1" spans="1:8">
       <c r="A702" t="s">
         <v>1475</v>
       </c>
@@ -32553,7 +32549,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="703" spans="1:8">
+    <row r="703" hidden="1" spans="1:8">
       <c r="A703" t="s">
         <v>1468</v>
       </c>
@@ -32579,7 +32575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="704" spans="1:8">
+    <row r="704" hidden="1" spans="1:8">
       <c r="A704" t="s">
         <v>1472</v>
       </c>
@@ -32605,7 +32601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" hidden="1" spans="1:8">
       <c r="A705" t="s">
         <v>1479</v>
       </c>
@@ -32631,7 +32627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" hidden="1" spans="1:8">
       <c r="A706" t="s">
         <v>1468</v>
       </c>
@@ -32657,7 +32653,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="707" spans="1:8">
+    <row r="707" hidden="1" spans="1:8">
       <c r="A707" t="s">
         <v>1472</v>
       </c>
@@ -32683,7 +32679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="708" spans="1:8">
+    <row r="708" hidden="1" spans="1:8">
       <c r="A708" t="s">
         <v>1475</v>
       </c>
@@ -32709,7 +32705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="709" spans="1:8">
+    <row r="709" hidden="1" spans="1:8">
       <c r="A709" t="s">
         <v>1479</v>
       </c>
@@ -32735,7 +32731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="710" spans="1:8">
+    <row r="710" hidden="1" spans="1:8">
       <c r="A710" t="s">
         <v>1468</v>
       </c>
@@ -32761,7 +32757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="711" spans="1:8">
+    <row r="711" hidden="1" spans="1:8">
       <c r="A711" t="s">
         <v>1472</v>
       </c>
@@ -32787,7 +32783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="712" spans="1:8">
+    <row r="712" hidden="1" spans="1:8">
       <c r="A712" t="s">
         <v>1475</v>
       </c>
@@ -32813,7 +32809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="713" spans="1:8">
+    <row r="713" hidden="1" spans="1:8">
       <c r="A713" t="s">
         <v>1479</v>
       </c>
@@ -32839,7 +32835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="714" spans="1:8">
+    <row r="714" hidden="1" spans="1:8">
       <c r="A714" t="s">
         <v>554</v>
       </c>
@@ -32865,7 +32861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="715" spans="1:8">
+    <row r="715" hidden="1" spans="1:8">
       <c r="A715" t="s">
         <v>539</v>
       </c>
@@ -32891,7 +32887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="716" spans="1:8">
+    <row r="716" hidden="1" spans="1:8">
       <c r="A716" t="s">
         <v>552</v>
       </c>
@@ -32917,7 +32913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="717" spans="1:8">
+    <row r="717" hidden="1" spans="1:8">
       <c r="A717" t="s">
         <v>550</v>
       </c>
@@ -32943,7 +32939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="718" spans="1:8">
+    <row r="718" hidden="1" spans="1:8">
       <c r="A718" t="s">
         <v>542</v>
       </c>
@@ -32969,7 +32965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="719" spans="1:8">
+    <row r="719" hidden="1" spans="1:8">
       <c r="A719" t="s">
         <v>527</v>
       </c>
@@ -32995,7 +32991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="720" spans="1:8">
+    <row r="720" hidden="1" spans="1:8">
       <c r="A720" t="s">
         <v>532</v>
       </c>
@@ -33021,7 +33017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="721" spans="1:8">
+    <row r="721" hidden="1" spans="1:8">
       <c r="A721" t="s">
         <v>545</v>
       </c>
@@ -33047,7 +33043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="722" spans="1:8">
+    <row r="722" hidden="1" spans="1:8">
       <c r="A722" t="s">
         <v>520</v>
       </c>
@@ -33073,7 +33069,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="723" spans="1:8">
+    <row r="723" hidden="1" spans="1:8">
       <c r="A723" t="s">
         <v>556</v>
       </c>
@@ -33099,7 +33095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="724" spans="1:8">
+    <row r="724" hidden="1" spans="1:8">
       <c r="A724" t="s">
         <v>548</v>
       </c>
@@ -33125,7 +33121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="725" spans="1:8">
+    <row r="725" hidden="1" spans="1:8">
       <c r="A725" t="s">
         <v>532</v>
       </c>
@@ -33151,7 +33147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="726" spans="1:8">
+    <row r="726" hidden="1" spans="1:8">
       <c r="A726" t="s">
         <v>554</v>
       </c>
@@ -33177,7 +33173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="727" spans="1:8">
+    <row r="727" hidden="1" spans="1:8">
       <c r="A727" t="s">
         <v>548</v>
       </c>
@@ -33203,7 +33199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="728" spans="1:8">
+    <row r="728" hidden="1" spans="1:8">
       <c r="A728" t="s">
         <v>542</v>
       </c>
@@ -33229,7 +33225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="729" spans="1:8">
+    <row r="729" hidden="1" spans="1:8">
       <c r="A729" t="s">
         <v>550</v>
       </c>
@@ -33255,7 +33251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="730" spans="1:8">
+    <row r="730" hidden="1" spans="1:8">
       <c r="A730" t="s">
         <v>556</v>
       </c>
@@ -33281,7 +33277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="731" spans="1:8">
+    <row r="731" hidden="1" spans="1:8">
       <c r="A731" t="s">
         <v>520</v>
       </c>
@@ -33307,7 +33303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="732" spans="1:8">
+    <row r="732" hidden="1" spans="1:8">
       <c r="A732" t="s">
         <v>539</v>
       </c>
@@ -33333,7 +33329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="733" spans="1:8">
+    <row r="733" hidden="1" spans="1:8">
       <c r="A733" t="s">
         <v>552</v>
       </c>
@@ -33359,7 +33355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="734" spans="1:8">
+    <row r="734" hidden="1" spans="1:8">
       <c r="A734" t="s">
         <v>545</v>
       </c>
@@ -33385,7 +33381,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="735" spans="1:8">
+    <row r="735" hidden="1" spans="1:8">
       <c r="A735" t="s">
         <v>527</v>
       </c>
@@ -33411,7 +33407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="736" spans="1:8">
+    <row r="736" hidden="1" spans="1:8">
       <c r="A736" t="s">
         <v>554</v>
       </c>
@@ -33437,7 +33433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="737" spans="1:8">
+    <row r="737" hidden="1" spans="1:8">
       <c r="A737" t="s">
         <v>548</v>
       </c>
@@ -33463,7 +33459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="738" spans="1:8">
+    <row r="738" hidden="1" spans="1:8">
       <c r="A738" t="s">
         <v>542</v>
       </c>
@@ -33489,7 +33485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="739" spans="1:8">
+    <row r="739" hidden="1" spans="1:8">
       <c r="A739" t="s">
         <v>550</v>
       </c>
@@ -33515,7 +33511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="740" spans="1:8">
+    <row r="740" hidden="1" spans="1:8">
       <c r="A740" t="s">
         <v>556</v>
       </c>
@@ -33541,7 +33537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="741" spans="1:8">
+    <row r="741" hidden="1" spans="1:8">
       <c r="A741" t="s">
         <v>520</v>
       </c>
@@ -33567,7 +33563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="742" spans="1:8">
+    <row r="742" hidden="1" spans="1:8">
       <c r="A742" t="s">
         <v>539</v>
       </c>
@@ -33593,7 +33589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="743" spans="1:8">
+    <row r="743" hidden="1" spans="1:8">
       <c r="A743" t="s">
         <v>552</v>
       </c>
@@ -33619,7 +33615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="744" spans="1:8">
+    <row r="744" hidden="1" spans="1:8">
       <c r="A744" t="s">
         <v>545</v>
       </c>
@@ -33645,7 +33641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" spans="1:8">
+    <row r="745" hidden="1" spans="1:8">
       <c r="A745" t="s">
         <v>527</v>
       </c>
@@ -33671,7 +33667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="746" spans="1:8">
+    <row r="746" hidden="1" spans="1:8">
       <c r="A746" t="s">
         <v>532</v>
       </c>
@@ -33697,7 +33693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="747" spans="1:8">
+    <row r="747" hidden="1" spans="1:8">
       <c r="A747" t="s">
         <v>554</v>
       </c>
@@ -33723,7 +33719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="748" spans="1:8">
+    <row r="748" hidden="1" spans="1:8">
       <c r="A748" t="s">
         <v>548</v>
       </c>
@@ -33749,7 +33745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="749" spans="1:8">
+    <row r="749" hidden="1" spans="1:8">
       <c r="A749" t="s">
         <v>542</v>
       </c>
@@ -33775,7 +33771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="750" spans="1:8">
+    <row r="750" hidden="1" spans="1:8">
       <c r="A750" t="s">
         <v>550</v>
       </c>
@@ -33801,7 +33797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="751" spans="1:8">
+    <row r="751" hidden="1" spans="1:8">
       <c r="A751" t="s">
         <v>556</v>
       </c>
@@ -33827,7 +33823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="752" spans="1:8">
+    <row r="752" hidden="1" spans="1:8">
       <c r="A752" t="s">
         <v>539</v>
       </c>
@@ -33853,7 +33849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="753" spans="1:8">
+    <row r="753" hidden="1" spans="1:8">
       <c r="A753" t="s">
         <v>552</v>
       </c>
@@ -33879,7 +33875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="754" spans="1:8">
+    <row r="754" hidden="1" spans="1:8">
       <c r="A754" t="s">
         <v>545</v>
       </c>
@@ -33905,7 +33901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="755" spans="1:8">
+    <row r="755" hidden="1" spans="1:8">
       <c r="A755" t="s">
         <v>527</v>
       </c>
@@ -33931,7 +33927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="756" spans="1:8">
+    <row r="756" hidden="1" spans="1:8">
       <c r="A756" t="s">
         <v>461</v>
       </c>
@@ -33957,7 +33953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="757" spans="1:8">
+    <row r="757" hidden="1" spans="1:8">
       <c r="A757" t="s">
         <v>461</v>
       </c>
@@ -33983,7 +33979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="758" spans="1:8">
+    <row r="758" hidden="1" spans="1:8">
       <c r="A758" t="s">
         <v>1533</v>
       </c>
@@ -34009,7 +34005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="759" spans="1:8">
+    <row r="759" hidden="1" spans="1:8">
       <c r="A759" t="s">
         <v>1533</v>
       </c>
@@ -34035,7 +34031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="760" spans="1:8">
+    <row r="760" hidden="1" spans="1:8">
       <c r="A760" t="s">
         <v>1533</v>
       </c>
@@ -34061,7 +34057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="761" spans="1:8">
+    <row r="761" hidden="1" spans="1:8">
       <c r="A761" t="s">
         <v>1533</v>
       </c>
@@ -34087,7 +34083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="762" spans="1:8">
+    <row r="762" hidden="1" spans="1:8">
       <c r="A762" t="s">
         <v>1533</v>
       </c>
@@ -34113,7 +34109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="763" spans="1:8">
+    <row r="763" hidden="1" spans="1:8">
       <c r="A763" t="s">
         <v>1533</v>
       </c>
@@ -34139,7 +34135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="764" spans="1:8">
+    <row r="764" hidden="1" spans="1:8">
       <c r="A764" t="s">
         <v>1533</v>
       </c>
@@ -34165,7 +34161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="765" spans="1:8">
+    <row r="765" hidden="1" spans="1:8">
       <c r="A765" t="s">
         <v>53</v>
       </c>
@@ -34191,7 +34187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="766" spans="1:8">
+    <row r="766" hidden="1" spans="1:8">
       <c r="A766" t="s">
         <v>53</v>
       </c>
@@ -34217,7 +34213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="767" spans="1:8">
+    <row r="767" hidden="1" spans="1:8">
       <c r="A767" t="s">
         <v>53</v>
       </c>
@@ -34243,7 +34239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="768" spans="1:8">
+    <row r="768" hidden="1" spans="1:8">
       <c r="A768" t="s">
         <v>53</v>
       </c>
@@ -34269,7 +34265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="769" spans="1:8">
+    <row r="769" hidden="1" spans="1:8">
       <c r="A769" t="s">
         <v>53</v>
       </c>
@@ -34295,7 +34291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="770" spans="1:8">
+    <row r="770" hidden="1" spans="1:8">
       <c r="A770" t="s">
         <v>53</v>
       </c>
@@ -34321,7 +34317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="771" spans="1:8">
+    <row r="771" hidden="1" spans="1:8">
       <c r="A771" t="s">
         <v>53</v>
       </c>
@@ -34347,7 +34343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="772" spans="1:8">
+    <row r="772" hidden="1" spans="1:8">
       <c r="A772" t="s">
         <v>57</v>
       </c>
@@ -34373,7 +34369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="773" spans="1:8">
+    <row r="773" hidden="1" spans="1:8">
       <c r="A773" t="s">
         <v>57</v>
       </c>
@@ -34399,7 +34395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="774" spans="1:8">
+    <row r="774" hidden="1" spans="1:8">
       <c r="A774" t="s">
         <v>70</v>
       </c>
@@ -34425,7 +34421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="775" spans="1:8">
+    <row r="775" hidden="1" spans="1:8">
       <c r="A775" t="s">
         <v>461</v>
       </c>
@@ -34451,7 +34447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="776" spans="1:8">
+    <row r="776" hidden="1" spans="1:8">
       <c r="A776" t="s">
         <v>984</v>
       </c>
@@ -34477,7 +34473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="777" spans="1:8">
+    <row r="777" hidden="1" spans="1:8">
       <c r="A777" t="s">
         <v>984</v>
       </c>
@@ -34503,7 +34499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="778" spans="1:8">
+    <row r="778" hidden="1" spans="1:8">
       <c r="A778" t="s">
         <v>984</v>
       </c>
@@ -34529,7 +34525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="779" spans="1:8">
+    <row r="779" hidden="1" spans="1:8">
       <c r="A779" t="s">
         <v>1570</v>
       </c>
@@ -34555,7 +34551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="780" spans="1:8">
+    <row r="780" hidden="1" spans="1:8">
       <c r="A780" t="s">
         <v>422</v>
       </c>
@@ -34581,7 +34577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="781" spans="1:8">
+    <row r="781" hidden="1" spans="1:8">
       <c r="A781" t="s">
         <v>422</v>
       </c>
@@ -34607,7 +34603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="782" spans="1:8">
+    <row r="782" hidden="1" spans="1:8">
       <c r="A782" t="s">
         <v>1577</v>
       </c>
@@ -34633,7 +34629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="783" spans="1:8">
+    <row r="783" hidden="1" spans="1:8">
       <c r="A783" t="s">
         <v>1577</v>
       </c>
@@ -34659,7 +34655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="784" spans="1:8">
+    <row r="784" hidden="1" spans="1:8">
       <c r="A784" t="s">
         <v>1577</v>
       </c>
@@ -34685,7 +34681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="785" spans="1:8">
+    <row r="785" hidden="1" spans="1:8">
       <c r="A785" t="s">
         <v>1123</v>
       </c>
@@ -34711,7 +34707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="786" spans="1:8">
+    <row r="786" hidden="1" spans="1:8">
       <c r="A786" t="s">
         <v>1123</v>
       </c>
@@ -34737,7 +34733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="787" spans="1:8">
+    <row r="787" hidden="1" spans="1:8">
       <c r="A787" t="s">
         <v>1123</v>
       </c>
@@ -34763,7 +34759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="788" spans="1:8">
+    <row r="788" hidden="1" spans="1:8">
       <c r="A788" t="s">
         <v>1123</v>
       </c>
@@ -34789,7 +34785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="789" spans="1:8">
+    <row r="789" hidden="1" spans="1:8">
       <c r="A789" t="s">
         <v>1589</v>
       </c>
@@ -34815,7 +34811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="790" spans="1:8">
+    <row r="790" hidden="1" spans="1:8">
       <c r="A790" t="s">
         <v>1592</v>
       </c>
@@ -34841,7 +34837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="791" spans="1:8">
+    <row r="791" hidden="1" spans="1:8">
       <c r="A791" t="s">
         <v>1592</v>
       </c>
@@ -34867,7 +34863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="792" spans="1:8">
+    <row r="792" hidden="1" spans="1:8">
       <c r="A792" t="s">
         <v>53</v>
       </c>
@@ -34893,7 +34889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="793" spans="1:8">
+    <row r="793" hidden="1" spans="1:8">
       <c r="A793" t="s">
         <v>65</v>
       </c>
@@ -34919,7 +34915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="794" spans="1:8">
+    <row r="794" hidden="1" spans="1:8">
       <c r="A794" t="s">
         <v>1603</v>
       </c>
@@ -34945,7 +34941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="795" spans="1:8">
+    <row r="795" hidden="1" spans="1:8">
       <c r="A795" t="s">
         <v>1603</v>
       </c>
@@ -34971,7 +34967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="796" spans="1:8">
+    <row r="796" hidden="1" spans="1:8">
       <c r="A796" t="s">
         <v>712</v>
       </c>
@@ -34997,7 +34993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="797" spans="1:8">
+    <row r="797" hidden="1" spans="1:8">
       <c r="A797" t="s">
         <v>712</v>
       </c>
@@ -35023,7 +35019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="798" spans="1:8">
+    <row r="798" hidden="1" spans="1:8">
       <c r="A798" t="s">
         <v>1613</v>
       </c>
@@ -35049,7 +35045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="799" spans="1:8">
+    <row r="799" hidden="1" spans="1:8">
       <c r="A799" t="s">
         <v>1613</v>
       </c>
@@ -35075,7 +35071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="800" spans="1:8">
+    <row r="800" hidden="1" spans="1:8">
       <c r="A800" t="s">
         <v>1617</v>
       </c>
@@ -35101,7 +35097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="801" spans="1:8">
+    <row r="801" hidden="1" spans="1:8">
       <c r="A801" t="s">
         <v>1617</v>
       </c>
@@ -35127,7 +35123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="802" spans="1:8">
+    <row r="802" hidden="1" spans="1:8">
       <c r="A802" t="s">
         <v>1617</v>
       </c>
@@ -35153,7 +35149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="803" spans="1:8">
+    <row r="803" hidden="1" spans="1:8">
       <c r="A803" t="s">
         <v>1617</v>
       </c>
@@ -35179,7 +35175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="804" spans="1:8">
+    <row r="804" hidden="1" spans="1:8">
       <c r="A804" t="s">
         <v>308</v>
       </c>
@@ -35205,7 +35201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="805" spans="1:8">
+    <row r="805" hidden="1" spans="1:8">
       <c r="A805" t="s">
         <v>308</v>
       </c>
@@ -35231,7 +35227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="806" spans="1:8">
+    <row r="806" hidden="1" spans="1:8">
       <c r="A806" t="s">
         <v>771</v>
       </c>
@@ -35257,7 +35253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="807" spans="1:8">
+    <row r="807" hidden="1" spans="1:8">
       <c r="A807" t="s">
         <v>771</v>
       </c>
@@ -35283,7 +35279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="808" spans="1:8">
+    <row r="808" hidden="1" spans="1:8">
       <c r="A808" t="s">
         <v>771</v>
       </c>
@@ -35309,7 +35305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="809" spans="1:8">
+    <row r="809" hidden="1" spans="1:8">
       <c r="A809" t="s">
         <v>771</v>
       </c>
@@ -35335,7 +35331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="810" spans="1:8">
+    <row r="810" hidden="1" spans="1:8">
       <c r="A810" t="s">
         <v>816</v>
       </c>
@@ -35361,7 +35357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="811" spans="1:8">
+    <row r="811" hidden="1" spans="1:8">
       <c r="A811" t="s">
         <v>816</v>
       </c>
@@ -35387,7 +35383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="812" spans="1:8">
+    <row r="812" hidden="1" spans="1:8">
       <c r="A812" t="s">
         <v>816</v>
       </c>
@@ -35413,7 +35409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="813" spans="1:8">
+    <row r="813" hidden="1" spans="1:8">
       <c r="A813" t="s">
         <v>816</v>
       </c>
@@ -35439,7 +35435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="814" spans="1:8">
+    <row r="814" hidden="1" spans="1:8">
       <c r="A814" t="s">
         <v>816</v>
       </c>
@@ -35465,7 +35461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="815" spans="1:8">
+    <row r="815" hidden="1" spans="1:8">
       <c r="A815" t="s">
         <v>308</v>
       </c>
@@ -35491,7 +35487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="816" spans="1:8">
+    <row r="816" hidden="1" spans="1:8">
       <c r="A816" t="s">
         <v>308</v>
       </c>
@@ -35517,7 +35513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="817" spans="1:8">
+    <row r="817" hidden="1" spans="1:8">
       <c r="A817" t="s">
         <v>308</v>
       </c>
@@ -35543,7 +35539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="818" spans="1:8">
+    <row r="818" hidden="1" spans="1:8">
       <c r="A818" t="s">
         <v>308</v>
       </c>
@@ -35569,7 +35565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="819" spans="1:8">
+    <row r="819" hidden="1" spans="1:8">
       <c r="A819" t="s">
         <v>308</v>
       </c>
@@ -35595,7 +35591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="820" spans="1:8">
+    <row r="820" hidden="1" spans="1:8">
       <c r="A820" t="s">
         <v>308</v>
       </c>
@@ -35621,7 +35617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="821" spans="1:8">
+    <row r="821" hidden="1" spans="1:8">
       <c r="A821" t="s">
         <v>308</v>
       </c>
@@ -35647,7 +35643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="822" spans="1:8">
+    <row r="822" hidden="1" spans="1:8">
       <c r="A822" t="s">
         <v>308</v>
       </c>
@@ -35673,7 +35669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="823" spans="1:8">
+    <row r="823" hidden="1" spans="1:8">
       <c r="A823" t="s">
         <v>308</v>
       </c>
@@ -35699,7 +35695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="824" spans="1:8">
+    <row r="824" hidden="1" spans="1:8">
       <c r="A824" t="s">
         <v>308</v>
       </c>
@@ -35725,7 +35721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="825" spans="1:8">
+    <row r="825" hidden="1" spans="1:8">
       <c r="A825" t="s">
         <v>308</v>
       </c>
@@ -35751,7 +35747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="826" spans="1:8">
+    <row r="826" hidden="1" spans="1:8">
       <c r="A826" t="s">
         <v>308</v>
       </c>
@@ -35777,7 +35773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="827" spans="1:8">
+    <row r="827" hidden="1" spans="1:8">
       <c r="A827" t="s">
         <v>308</v>
       </c>
@@ -35803,7 +35799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="828" spans="1:8">
+    <row r="828" hidden="1" spans="1:8">
       <c r="A828" t="s">
         <v>308</v>
       </c>
@@ -35829,7 +35825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="829" spans="1:8">
+    <row r="829" hidden="1" spans="1:8">
       <c r="A829" t="s">
         <v>1603</v>
       </c>
@@ -35855,7 +35851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="830" spans="1:8">
+    <row r="830" hidden="1" spans="1:8">
       <c r="A830" t="s">
         <v>1603</v>
       </c>
@@ -35881,7 +35877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="831" spans="1:8">
+    <row r="831" hidden="1" spans="1:8">
       <c r="A831" t="s">
         <v>1603</v>
       </c>
@@ -35907,7 +35903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="832" spans="1:8">
+    <row r="832" hidden="1" spans="1:8">
       <c r="A832" t="s">
         <v>1603</v>
       </c>
@@ -35933,7 +35929,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="833" spans="1:8">
+    <row r="833" hidden="1" spans="1:8">
       <c r="A833" t="s">
         <v>1603</v>
       </c>
@@ -35959,7 +35955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="834" spans="1:8">
+    <row r="834" hidden="1" spans="1:8">
       <c r="A834" t="s">
         <v>1603</v>
       </c>
@@ -35985,7 +35981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="835" spans="1:8">
+    <row r="835" hidden="1" spans="1:8">
       <c r="A835" t="s">
         <v>1603</v>
       </c>
@@ -36011,7 +36007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="836" spans="1:8">
+    <row r="836" hidden="1" spans="1:8">
       <c r="A836" t="s">
         <v>1603</v>
       </c>
@@ -36037,7 +36033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="837" spans="1:8">
+    <row r="837" hidden="1" spans="1:8">
       <c r="A837" t="s">
         <v>232</v>
       </c>
@@ -36063,7 +36059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="838" spans="1:8">
+    <row r="838" hidden="1" spans="1:8">
       <c r="A838" t="s">
         <v>111</v>
       </c>
@@ -36089,7 +36085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="839" spans="1:8">
+    <row r="839" hidden="1" spans="1:8">
       <c r="A839" t="s">
         <v>984</v>
       </c>
@@ -36115,7 +36111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="840" spans="1:8">
+    <row r="840" hidden="1" spans="1:8">
       <c r="A840" t="s">
         <v>771</v>
       </c>
@@ -36141,7 +36137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="841" spans="1:8">
+    <row r="841" hidden="1" spans="1:8">
       <c r="A841" t="s">
         <v>771</v>
       </c>
@@ -36167,7 +36163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="842" spans="1:8">
+    <row r="842" hidden="1" spans="1:8">
       <c r="A842" t="s">
         <v>771</v>
       </c>
@@ -36193,7 +36189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="843" spans="1:8">
+    <row r="843" hidden="1" spans="1:8">
       <c r="A843" t="s">
         <v>771</v>
       </c>
@@ -36219,7 +36215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="844" spans="1:8">
+    <row r="844" hidden="1" spans="1:8">
       <c r="A844" t="s">
         <v>1699</v>
       </c>
@@ -36245,7 +36241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="845" spans="1:8">
+    <row r="845" hidden="1" spans="1:8">
       <c r="A845" t="s">
         <v>1699</v>
       </c>
@@ -36271,7 +36267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="846" spans="1:8">
+    <row r="846" hidden="1" spans="1:8">
       <c r="A846" t="s">
         <v>1699</v>
       </c>
@@ -36297,7 +36293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="847" spans="1:8">
+    <row r="847" hidden="1" spans="1:8">
       <c r="A847" t="s">
         <v>1699</v>
       </c>
@@ -36323,7 +36319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="848" spans="1:8">
+    <row r="848" hidden="1" spans="1:8">
       <c r="A848" t="s">
         <v>1699</v>
       </c>
@@ -36349,7 +36345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="849" spans="1:8">
+    <row r="849" hidden="1" spans="1:8">
       <c r="A849" t="s">
         <v>1699</v>
       </c>
@@ -36375,7 +36371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="850" spans="1:8">
+    <row r="850" hidden="1" spans="1:8">
       <c r="A850" t="s">
         <v>1699</v>
       </c>
@@ -36401,7 +36397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="851" spans="1:8">
+    <row r="851" hidden="1" spans="1:8">
       <c r="A851" t="s">
         <v>1699</v>
       </c>
@@ -36427,7 +36423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="852" spans="1:8">
+    <row r="852" hidden="1" spans="1:8">
       <c r="A852" t="s">
         <v>1699</v>
       </c>
@@ -36453,7 +36449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="853" spans="1:8">
+    <row r="853" hidden="1" spans="1:8">
       <c r="A853" t="s">
         <v>1699</v>
       </c>
@@ -36479,7 +36475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="854" spans="1:8">
+    <row r="854" hidden="1" spans="1:8">
       <c r="A854" t="s">
         <v>1699</v>
       </c>
@@ -36505,7 +36501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="855" spans="1:8">
+    <row r="855" hidden="1" spans="1:8">
       <c r="A855" t="s">
         <v>1613</v>
       </c>
@@ -36531,7 +36527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="856" spans="1:8">
+    <row r="856" hidden="1" spans="1:8">
       <c r="A856" t="s">
         <v>1613</v>
       </c>
@@ -36557,7 +36553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="857" spans="1:8">
+    <row r="857" hidden="1" spans="1:8">
       <c r="A857" t="s">
         <v>1613</v>
       </c>
@@ -36583,7 +36579,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="858" spans="1:8">
+    <row r="858" hidden="1" spans="1:8">
       <c r="A858" t="s">
         <v>1613</v>
       </c>
@@ -36609,7 +36605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="859" spans="1:8">
+    <row r="859" hidden="1" spans="1:8">
       <c r="A859" t="s">
         <v>53</v>
       </c>
@@ -36635,7 +36631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="860" spans="1:8">
+    <row r="860" hidden="1" spans="1:8">
       <c r="A860" t="s">
         <v>635</v>
       </c>
@@ -36661,7 +36657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="861" spans="1:8">
+    <row r="861" hidden="1" spans="1:8">
       <c r="A861" t="s">
         <v>635</v>
       </c>
@@ -36687,7 +36683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="862" spans="1:8">
+    <row r="862" hidden="1" spans="1:8">
       <c r="A862" t="s">
         <v>635</v>
       </c>
@@ -36713,7 +36709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="863" spans="1:8">
+    <row r="863" hidden="1" spans="1:8">
       <c r="A863" t="s">
         <v>270</v>
       </c>
@@ -36739,7 +36735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="864" spans="1:8">
+    <row r="864" hidden="1" spans="1:8">
       <c r="A864" t="s">
         <v>270</v>
       </c>
@@ -36765,7 +36761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="865" spans="1:8">
+    <row r="865" hidden="1" spans="1:8">
       <c r="A865" t="s">
         <v>811</v>
       </c>
@@ -36791,7 +36787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="866" spans="1:8">
+    <row r="866" hidden="1" spans="1:8">
       <c r="A866" t="s">
         <v>811</v>
       </c>
@@ -36817,7 +36813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="867" spans="1:8">
+    <row r="867" hidden="1" spans="1:8">
       <c r="A867" t="s">
         <v>811</v>
       </c>
@@ -36843,7 +36839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="868" spans="1:8">
+    <row r="868" hidden="1" spans="1:8">
       <c r="A868" t="s">
         <v>811</v>
       </c>
@@ -36869,7 +36865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="869" spans="1:8">
+    <row r="869" hidden="1" spans="1:8">
       <c r="A869" t="s">
         <v>811</v>
       </c>
@@ -36895,7 +36891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="870" spans="1:8">
+    <row r="870" hidden="1" spans="1:8">
       <c r="A870" t="s">
         <v>811</v>
       </c>
@@ -36921,7 +36917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="871" spans="1:8">
+    <row r="871" hidden="1" spans="1:8">
       <c r="A871" t="s">
         <v>811</v>
       </c>
@@ -36947,7 +36943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="872" spans="1:8">
+    <row r="872" hidden="1" spans="1:8">
       <c r="A872" t="s">
         <v>811</v>
       </c>
@@ -36973,7 +36969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="873" spans="1:8">
+    <row r="873" hidden="1" spans="1:8">
       <c r="A873" t="s">
         <v>811</v>
       </c>
@@ -36999,7 +36995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="874" spans="1:8">
+    <row r="874" hidden="1" spans="1:8">
       <c r="A874" t="s">
         <v>811</v>
       </c>
@@ -37025,7 +37021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="875" spans="1:8">
+    <row r="875" hidden="1" spans="1:8">
       <c r="A875" t="s">
         <v>811</v>
       </c>
@@ -37051,7 +37047,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="876" spans="1:8">
+    <row r="876" hidden="1" spans="1:8">
       <c r="A876" t="s">
         <v>811</v>
       </c>
@@ -37077,7 +37073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="877" spans="1:8">
+    <row r="877" hidden="1" spans="1:8">
       <c r="A877" t="s">
         <v>811</v>
       </c>
@@ -37103,7 +37099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="878" spans="1:8">
+    <row r="878" hidden="1" spans="1:8">
       <c r="A878" t="s">
         <v>811</v>
       </c>
@@ -37129,7 +37125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="879" spans="1:8">
+    <row r="879" hidden="1" spans="1:8">
       <c r="A879" t="s">
         <v>811</v>
       </c>
@@ -37155,7 +37151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="880" spans="1:8">
+    <row r="880" hidden="1" spans="1:8">
       <c r="A880" t="s">
         <v>622</v>
       </c>
@@ -37181,7 +37177,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="881" spans="1:8">
+    <row r="881" hidden="1" spans="1:8">
       <c r="A881" t="s">
         <v>622</v>
       </c>
@@ -37207,7 +37203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="882" spans="1:8">
+    <row r="882" hidden="1" spans="1:8">
       <c r="A882" t="s">
         <v>622</v>
       </c>
@@ -37233,7 +37229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="883" spans="1:8">
+    <row r="883" hidden="1" spans="1:8">
       <c r="A883" t="s">
         <v>622</v>
       </c>
@@ -37259,7 +37255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="884" spans="1:8">
+    <row r="884" hidden="1" spans="1:8">
       <c r="A884" t="s">
         <v>622</v>
       </c>
@@ -37285,7 +37281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="885" spans="1:8">
+    <row r="885" hidden="1" spans="1:8">
       <c r="A885" t="s">
         <v>622</v>
       </c>
@@ -37311,7 +37307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="886" spans="1:8">
+    <row r="886" hidden="1" spans="1:8">
       <c r="A886" t="s">
         <v>629</v>
       </c>
@@ -37337,7 +37333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="887" spans="1:8">
+    <row r="887" hidden="1" spans="1:8">
       <c r="A887" t="s">
         <v>629</v>
       </c>
@@ -37363,7 +37359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="888" spans="1:8">
+    <row r="888" hidden="1" spans="1:8">
       <c r="A888" t="s">
         <v>629</v>
       </c>
@@ -37389,7 +37385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="889" spans="1:8">
+    <row r="889" hidden="1" spans="1:8">
       <c r="A889" t="s">
         <v>629</v>
       </c>
@@ -37415,7 +37411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="890" spans="1:8">
+    <row r="890" hidden="1" spans="1:8">
       <c r="A890" t="s">
         <v>629</v>
       </c>
@@ -37441,7 +37437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="891" spans="1:8">
+    <row r="891" hidden="1" spans="1:8">
       <c r="A891" t="s">
         <v>1419</v>
       </c>
@@ -37467,7 +37463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="892" spans="1:8">
+    <row r="892" hidden="1" spans="1:8">
       <c r="A892" t="s">
         <v>1419</v>
       </c>
@@ -37493,7 +37489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="893" spans="1:8">
+    <row r="893" hidden="1" spans="1:8">
       <c r="A893" t="s">
         <v>1419</v>
       </c>
@@ -37519,7 +37515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="894" spans="1:8">
+    <row r="894" hidden="1" spans="1:8">
       <c r="A894" t="s">
         <v>736</v>
       </c>
@@ -37545,7 +37541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="895" spans="1:8">
+    <row r="895" hidden="1" spans="1:8">
       <c r="A895" t="s">
         <v>736</v>
       </c>
@@ -37571,7 +37567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="896" spans="1:8">
+    <row r="896" hidden="1" spans="1:8">
       <c r="A896" t="s">
         <v>736</v>
       </c>
@@ -37597,7 +37593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="897" spans="1:8">
+    <row r="897" hidden="1" spans="1:8">
       <c r="A897" t="s">
         <v>736</v>
       </c>
@@ -37623,7 +37619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="898" spans="1:8">
+    <row r="898" hidden="1" spans="1:8">
       <c r="A898" t="s">
         <v>736</v>
       </c>
@@ -37649,7 +37645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="899" spans="1:8">
+    <row r="899" hidden="1" spans="1:8">
       <c r="A899" t="s">
         <v>736</v>
       </c>
@@ -37675,7 +37671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="900" spans="1:8">
+    <row r="900" hidden="1" spans="1:8">
       <c r="A900" t="s">
         <v>736</v>
       </c>
@@ -37701,7 +37697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="901" spans="1:8">
+    <row r="901" hidden="1" spans="1:8">
       <c r="A901" t="s">
         <v>736</v>
       </c>
@@ -37727,7 +37723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="902" spans="1:8">
+    <row r="902" hidden="1" spans="1:8">
       <c r="A902" t="s">
         <v>736</v>
       </c>
@@ -37753,7 +37749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="903" spans="1:8">
+    <row r="903" hidden="1" spans="1:8">
       <c r="A903" t="s">
         <v>160</v>
       </c>
@@ -37779,7 +37775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="904" spans="1:8">
+    <row r="904" hidden="1" spans="1:8">
       <c r="A904" t="s">
         <v>160</v>
       </c>
@@ -37805,7 +37801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="905" spans="1:8">
+    <row r="905" hidden="1" spans="1:8">
       <c r="A905" t="s">
         <v>160</v>
       </c>
@@ -37831,7 +37827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="906" spans="1:8">
+    <row r="906" hidden="1" spans="1:8">
       <c r="A906" t="s">
         <v>160</v>
       </c>
@@ -37857,7 +37853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="907" spans="1:8">
+    <row r="907" hidden="1" spans="1:8">
       <c r="A907" t="s">
         <v>160</v>
       </c>
@@ -37883,7 +37879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="908" spans="1:8">
+    <row r="908" hidden="1" spans="1:8">
       <c r="A908" t="s">
         <v>160</v>
       </c>
@@ -37909,7 +37905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="909" spans="1:8">
+    <row r="909" hidden="1" spans="1:8">
       <c r="A909" t="s">
         <v>160</v>
       </c>
@@ -37935,7 +37931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="910" spans="1:8">
+    <row r="910" hidden="1" spans="1:8">
       <c r="A910" t="s">
         <v>160</v>
       </c>
@@ -37961,7 +37957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="911" spans="1:8">
+    <row r="911" hidden="1" spans="1:8">
       <c r="A911" t="s">
         <v>1750</v>
       </c>
@@ -37987,7 +37983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="912" spans="1:8">
+    <row r="912" hidden="1" spans="1:8">
       <c r="A912" t="s">
         <v>1750</v>
       </c>
@@ -38013,7 +38009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="913" spans="1:8">
+    <row r="913" hidden="1" spans="1:8">
       <c r="A913" t="s">
         <v>1750</v>
       </c>
@@ -38039,7 +38035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="914" spans="1:8">
+    <row r="914" hidden="1" spans="1:8">
       <c r="A914" t="s">
         <v>1577</v>
       </c>
@@ -38065,7 +38061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="915" spans="1:8">
+    <row r="915" hidden="1" spans="1:8">
       <c r="A915" t="s">
         <v>1577</v>
       </c>
@@ -38091,7 +38087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="916" spans="1:8">
+    <row r="916" hidden="1" spans="1:8">
       <c r="A916" t="s">
         <v>1577</v>
       </c>
@@ -38117,7 +38113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="917" spans="1:8">
+    <row r="917" hidden="1" spans="1:8">
       <c r="A917" t="s">
         <v>1577</v>
       </c>
@@ -38143,7 +38139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="918" spans="1:8">
+    <row r="918" hidden="1" spans="1:8">
       <c r="A918" t="s">
         <v>1577</v>
       </c>
@@ -38169,7 +38165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="919" spans="1:8">
+    <row r="919" hidden="1" spans="1:8">
       <c r="A919" t="s">
         <v>1592</v>
       </c>
@@ -38195,7 +38191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="920" spans="1:8">
+    <row r="920" hidden="1" spans="1:8">
       <c r="A920" t="s">
         <v>130</v>
       </c>
@@ -38221,7 +38217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="921" spans="1:8">
+    <row r="921" hidden="1" spans="1:8">
       <c r="A921" t="s">
         <v>130</v>
       </c>
@@ -38247,7 +38243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="922" spans="1:8">
+    <row r="922" hidden="1" spans="1:8">
       <c r="A922" t="s">
         <v>130</v>
       </c>
@@ -38273,7 +38269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="923" spans="1:8">
+    <row r="923" hidden="1" spans="1:8">
       <c r="A923" t="s">
         <v>130</v>
       </c>
@@ -38299,7 +38295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="924" spans="1:8">
+    <row r="924" hidden="1" spans="1:8">
       <c r="A924" t="s">
         <v>130</v>
       </c>
@@ -38325,7 +38321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="925" spans="1:8">
+    <row r="925" hidden="1" spans="1:8">
       <c r="A925" t="s">
         <v>130</v>
       </c>
@@ -38351,7 +38347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="926" spans="1:8">
+    <row r="926" hidden="1" spans="1:8">
       <c r="A926" t="s">
         <v>130</v>
       </c>
@@ -38377,7 +38373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="927" spans="1:8">
+    <row r="927" hidden="1" spans="1:8">
       <c r="A927" t="s">
         <v>130</v>
       </c>
@@ -38403,7 +38399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="928" spans="1:8">
+    <row r="928" hidden="1" spans="1:8">
       <c r="A928" t="s">
         <v>130</v>
       </c>
@@ -38429,7 +38425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="929" spans="1:8">
+    <row r="929" hidden="1" spans="1:8">
       <c r="A929" t="s">
         <v>130</v>
       </c>
@@ -38455,7 +38451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="930" spans="1:8">
+    <row r="930" hidden="1" spans="1:8">
       <c r="A930" t="s">
         <v>1755</v>
       </c>
@@ -38481,7 +38477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="931" spans="1:8">
+    <row r="931" hidden="1" spans="1:8">
       <c r="A931" t="s">
         <v>1759</v>
       </c>
@@ -38507,7 +38503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="932" spans="1:8">
+    <row r="932" hidden="1" spans="1:8">
       <c r="A932" t="s">
         <v>1759</v>
       </c>
@@ -38533,7 +38529,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="933" spans="1:8">
+    <row r="933" hidden="1" spans="1:8">
       <c r="A933" t="s">
         <v>1759</v>
       </c>
@@ -38559,7 +38555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="934" spans="1:8">
+    <row r="934" hidden="1" spans="1:8">
       <c r="A934" t="s">
         <v>1759</v>
       </c>
@@ -38585,7 +38581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="935" spans="1:8">
+    <row r="935" hidden="1" spans="1:8">
       <c r="A935" t="s">
         <v>1759</v>
       </c>
@@ -38611,7 +38607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="936" spans="1:8">
+    <row r="936" hidden="1" spans="1:8">
       <c r="A936" t="s">
         <v>1759</v>
       </c>
@@ -38637,7 +38633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="937" spans="1:8">
+    <row r="937" hidden="1" spans="1:8">
       <c r="A937" t="s">
         <v>1759</v>
       </c>
@@ -38663,7 +38659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="938" spans="1:8">
+    <row r="938" hidden="1" spans="1:8">
       <c r="A938" t="s">
         <v>1759</v>
       </c>
@@ -38689,7 +38685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="939" spans="1:8">
+    <row r="939" hidden="1" spans="1:8">
       <c r="A939" t="s">
         <v>1759</v>
       </c>
@@ -38715,7 +38711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="940" spans="1:8">
+    <row r="940" hidden="1" spans="1:8">
       <c r="A940" t="s">
         <v>1759</v>
       </c>
@@ -38741,7 +38737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="941" spans="1:8">
+    <row r="941" hidden="1" spans="1:8">
       <c r="A941" t="s">
         <v>1759</v>
       </c>
@@ -38767,7 +38763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="942" spans="1:8">
+    <row r="942" hidden="1" spans="1:8">
       <c r="A942" t="s">
         <v>1759</v>
       </c>
@@ -38793,7 +38789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="943" spans="1:8">
+    <row r="943" hidden="1" spans="1:8">
       <c r="A943" t="s">
         <v>1759</v>
       </c>
@@ -38819,7 +38815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="944" spans="1:8">
+    <row r="944" hidden="1" spans="1:8">
       <c r="A944" t="s">
         <v>1759</v>
       </c>
@@ -38845,7 +38841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="945" spans="1:8">
+    <row r="945" hidden="1" spans="1:8">
       <c r="A945" t="s">
         <v>1759</v>
       </c>
@@ -38871,7 +38867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="946" spans="1:8">
+    <row r="946" hidden="1" spans="1:8">
       <c r="A946" t="s">
         <v>1759</v>
       </c>
@@ -38897,7 +38893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="947" spans="1:8">
+    <row r="947" hidden="1" spans="1:8">
       <c r="A947" t="s">
         <v>30</v>
       </c>
@@ -38923,7 +38919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="948" spans="1:8">
+    <row r="948" hidden="1" spans="1:8">
       <c r="A948" t="s">
         <v>30</v>
       </c>
@@ -38949,7 +38945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="949" spans="1:8">
+    <row r="949" hidden="1" spans="1:8">
       <c r="A949" t="s">
         <v>30</v>
       </c>
@@ -38975,7 +38971,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="950" spans="1:8">
+    <row r="950" hidden="1" spans="1:8">
       <c r="A950" t="s">
         <v>30</v>
       </c>
@@ -39001,7 +38997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="951" spans="1:8">
+    <row r="951" hidden="1" spans="1:8">
       <c r="A951" t="s">
         <v>1765</v>
       </c>
@@ -39027,7 +39023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="952" spans="1:8">
+    <row r="952" hidden="1" spans="1:8">
       <c r="A952" t="s">
         <v>1765</v>
       </c>
@@ -39053,7 +39049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="953" spans="1:8">
+    <row r="953" hidden="1" spans="1:8">
       <c r="A953" t="s">
         <v>1463</v>
       </c>
@@ -39079,7 +39075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="954" spans="1:8">
+    <row r="954" hidden="1" spans="1:8">
       <c r="A954" t="s">
         <v>1463</v>
       </c>
@@ -39105,7 +39101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="955" spans="1:8">
+    <row r="955" hidden="1" spans="1:8">
       <c r="A955" t="s">
         <v>1463</v>
       </c>
@@ -39131,7 +39127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="956" spans="1:8">
+    <row r="956" hidden="1" spans="1:8">
       <c r="A956" t="s">
         <v>1463</v>
       </c>
@@ -39157,7 +39153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="957" spans="1:8">
+    <row r="957" hidden="1" spans="1:8">
       <c r="A957" t="s">
         <v>1463</v>
       </c>
@@ -39183,7 +39179,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="958" spans="1:8">
+    <row r="958" hidden="1" spans="1:8">
       <c r="A958" t="s">
         <v>1463</v>
       </c>
@@ -39209,7 +39205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="959" spans="1:8">
+    <row r="959" hidden="1" spans="1:8">
       <c r="A959" t="s">
         <v>1463</v>
       </c>
@@ -39235,7 +39231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="960" spans="1:8">
+    <row r="960" hidden="1" spans="1:8">
       <c r="A960" t="s">
         <v>1463</v>
       </c>
@@ -39261,7 +39257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="961" spans="1:8">
+    <row r="961" hidden="1" spans="1:8">
       <c r="A961" t="s">
         <v>1463</v>
       </c>
@@ -39287,7 +39283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="962" spans="1:8">
+    <row r="962" hidden="1" spans="1:8">
       <c r="A962" t="s">
         <v>1463</v>
       </c>
@@ -39313,7 +39309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="963" spans="1:8">
+    <row r="963" hidden="1" spans="1:8">
       <c r="A963" t="s">
         <v>1130</v>
       </c>
@@ -39339,7 +39335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="964" spans="1:8">
+    <row r="964" hidden="1" spans="1:8">
       <c r="A964" t="s">
         <v>1130</v>
       </c>
@@ -39365,7 +39361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="965" spans="1:8">
+    <row r="965" hidden="1" spans="1:8">
       <c r="A965" t="s">
         <v>148</v>
       </c>
@@ -39391,7 +39387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="966" spans="1:8">
+    <row r="966" hidden="1" spans="1:8">
       <c r="A966" t="s">
         <v>148</v>
       </c>
@@ -39417,7 +39413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="967" spans="1:8">
+    <row r="967" hidden="1" spans="1:8">
       <c r="A967" t="s">
         <v>148</v>
       </c>
@@ -39443,7 +39439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="968" spans="1:8">
+    <row r="968" hidden="1" spans="1:8">
       <c r="A968" t="s">
         <v>148</v>
       </c>
@@ -39469,7 +39465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="969" spans="1:8">
+    <row r="969" hidden="1" spans="1:8">
       <c r="A969" t="s">
         <v>148</v>
       </c>
@@ -39495,7 +39491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="970" spans="1:8">
+    <row r="970" hidden="1" spans="1:8">
       <c r="A970" t="s">
         <v>148</v>
       </c>
@@ -39521,7 +39517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="971" spans="1:8">
+    <row r="971" hidden="1" spans="1:8">
       <c r="A971" t="s">
         <v>148</v>
       </c>
@@ -39547,7 +39543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="972" spans="1:8">
+    <row r="972" hidden="1" spans="1:8">
       <c r="A972" t="s">
         <v>148</v>
       </c>
@@ -39573,7 +39569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="973" spans="1:8">
+    <row r="973" hidden="1" spans="1:8">
       <c r="A973" t="s">
         <v>148</v>
       </c>
@@ -39599,7 +39595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="974" spans="1:8">
+    <row r="974" hidden="1" spans="1:8">
       <c r="A974" t="s">
         <v>1769</v>
       </c>
@@ -39625,7 +39621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="975" spans="1:8">
+    <row r="975" hidden="1" spans="1:8">
       <c r="A975" t="s">
         <v>1769</v>
       </c>
@@ -39651,7 +39647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="976" spans="1:8">
+    <row r="976" hidden="1" spans="1:8">
       <c r="A976" t="s">
         <v>1769</v>
       </c>
@@ -39677,7 +39673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="977" spans="1:8">
+    <row r="977" hidden="1" spans="1:8">
       <c r="A977" t="s">
         <v>1769</v>
       </c>
@@ -39703,7 +39699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="978" spans="1:8">
+    <row r="978" hidden="1" spans="1:8">
       <c r="A978" t="s">
         <v>1769</v>
       </c>
@@ -39729,7 +39725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="979" spans="1:8">
+    <row r="979" hidden="1" spans="1:8">
       <c r="A979" t="s">
         <v>640</v>
       </c>
@@ -39755,7 +39751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="980" spans="1:8">
+    <row r="980" hidden="1" spans="1:8">
       <c r="A980" t="s">
         <v>640</v>
       </c>
@@ -39781,7 +39777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="981" spans="1:8">
+    <row r="981" hidden="1" spans="1:8">
       <c r="A981" t="s">
         <v>640</v>
       </c>
@@ -39807,7 +39803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="982" spans="1:8">
+    <row r="982" hidden="1" spans="1:8">
       <c r="A982" t="s">
         <v>640</v>
       </c>
@@ -39833,7 +39829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="983" spans="1:8">
+    <row r="983" hidden="1" spans="1:8">
       <c r="A983" t="s">
         <v>156</v>
       </c>
@@ -39859,7 +39855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="984" spans="1:8">
+    <row r="984" hidden="1" spans="1:8">
       <c r="A984" t="s">
         <v>156</v>
       </c>
@@ -39885,7 +39881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="985" spans="1:8">
+    <row r="985" hidden="1" spans="1:8">
       <c r="A985" t="s">
         <v>156</v>
       </c>
@@ -39911,7 +39907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="986" spans="1:8">
+    <row r="986" hidden="1" spans="1:8">
       <c r="A986" t="s">
         <v>156</v>
       </c>
@@ -39937,7 +39933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="987" spans="1:8">
+    <row r="987" hidden="1" spans="1:8">
       <c r="A987" t="s">
         <v>156</v>
       </c>
@@ -39963,7 +39959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="988" spans="1:8">
+    <row r="988" hidden="1" spans="1:8">
       <c r="A988" t="s">
         <v>156</v>
       </c>
@@ -39989,7 +39985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="989" spans="1:8">
+    <row r="989" hidden="1" spans="1:8">
       <c r="A989" t="s">
         <v>156</v>
       </c>
@@ -40015,7 +40011,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="990" spans="1:8">
+    <row r="990" hidden="1" spans="1:8">
       <c r="A990" t="s">
         <v>156</v>
       </c>
@@ -40041,7 +40037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="991" spans="1:8">
+    <row r="991" hidden="1" spans="1:8">
       <c r="A991" t="s">
         <v>156</v>
       </c>
@@ -40067,7 +40063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="992" spans="1:8">
+    <row r="992" hidden="1" spans="1:8">
       <c r="A992" t="s">
         <v>1479</v>
       </c>
@@ -40093,7 +40089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="993" spans="1:8">
+    <row r="993" hidden="1" spans="1:8">
       <c r="A993" t="s">
         <v>1781</v>
       </c>
@@ -40119,7 +40115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="994" spans="1:8">
+    <row r="994" hidden="1" spans="1:8">
       <c r="A994" t="s">
         <v>1781</v>
       </c>
@@ -40145,7 +40141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="995" spans="1:8">
+    <row r="995" hidden="1" spans="1:8">
       <c r="A995" t="s">
         <v>1781</v>
       </c>
@@ -40171,7 +40167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="996" spans="1:8">
+    <row r="996" hidden="1" spans="1:8">
       <c r="A996" t="s">
         <v>1781</v>
       </c>
@@ -40197,7 +40193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="997" spans="1:8">
+    <row r="997" hidden="1" spans="1:8">
       <c r="A997" t="s">
         <v>1783</v>
       </c>
@@ -40223,7 +40219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="998" spans="1:8">
+    <row r="998" hidden="1" spans="1:8">
       <c r="A998" t="s">
         <v>1783</v>
       </c>
@@ -40249,7 +40245,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="999" spans="1:8">
+    <row r="999" hidden="1" spans="1:8">
       <c r="A999" t="s">
         <v>1783</v>
       </c>
@@ -40275,7 +40271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1000" spans="1:8">
+    <row r="1000" hidden="1" spans="1:8">
       <c r="A1000" t="s">
         <v>1783</v>
       </c>
@@ -40301,7 +40297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1001" spans="1:8">
+    <row r="1001" hidden="1" spans="1:8">
       <c r="A1001" t="s">
         <v>1783</v>
       </c>
@@ -40327,7 +40323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1002" spans="1:8">
+    <row r="1002" hidden="1" spans="1:8">
       <c r="A1002" t="s">
         <v>811</v>
       </c>
@@ -40353,7 +40349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1003" spans="1:8">
+    <row r="1003" hidden="1" spans="1:8">
       <c r="A1003" t="s">
         <v>811</v>
       </c>
@@ -40379,7 +40375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1004" spans="1:8">
+    <row r="1004" hidden="1" spans="1:8">
       <c r="A1004" t="s">
         <v>811</v>
       </c>
@@ -40405,7 +40401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1005" spans="1:8">
+    <row r="1005" hidden="1" spans="1:8">
       <c r="A1005" t="s">
         <v>811</v>
       </c>
@@ -40431,7 +40427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1006" spans="1:8">
+    <row r="1006" hidden="1" spans="1:8">
       <c r="A1006" t="s">
         <v>811</v>
       </c>
@@ -40457,7 +40453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1007" spans="1:8">
+    <row r="1007" hidden="1" spans="1:8">
       <c r="A1007" t="s">
         <v>811</v>
       </c>
@@ -40483,7 +40479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1008" spans="1:8">
+    <row r="1008" hidden="1" spans="1:8">
       <c r="A1008" t="s">
         <v>811</v>
       </c>
@@ -40509,7 +40505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1009" spans="1:8">
+    <row r="1009" hidden="1" spans="1:8">
       <c r="A1009" t="s">
         <v>811</v>
       </c>
@@ -40535,7 +40531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1010" spans="1:8">
+    <row r="1010" hidden="1" spans="1:8">
       <c r="A1010" t="s">
         <v>811</v>
       </c>
@@ -40561,7 +40557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1011" spans="1:8">
+    <row r="1011" hidden="1" spans="1:8">
       <c r="A1011" t="s">
         <v>811</v>
       </c>
@@ -40587,7 +40583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1012" spans="1:8">
+    <row r="1012" hidden="1" spans="1:8">
       <c r="A1012" t="s">
         <v>811</v>
       </c>
@@ -40613,7 +40609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1013" spans="1:8">
+    <row r="1013" hidden="1" spans="1:8">
       <c r="A1013" t="s">
         <v>811</v>
       </c>
@@ -40639,7 +40635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1014" spans="1:8">
+    <row r="1014" hidden="1" spans="1:8">
       <c r="A1014" t="s">
         <v>811</v>
       </c>
@@ -40665,7 +40661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1015" spans="1:8">
+    <row r="1015" hidden="1" spans="1:8">
       <c r="A1015" t="s">
         <v>811</v>
       </c>
@@ -40691,7 +40687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1016" spans="1:8">
+    <row r="1016" hidden="1" spans="1:8">
       <c r="A1016" t="s">
         <v>811</v>
       </c>
@@ -40717,7 +40713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1017" spans="1:8">
+    <row r="1017" hidden="1" spans="1:8">
       <c r="A1017" t="s">
         <v>1785</v>
       </c>
@@ -40743,7 +40739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1018" spans="1:8">
+    <row r="1018" hidden="1" spans="1:8">
       <c r="A1018" t="s">
         <v>1785</v>
       </c>
@@ -40769,7 +40765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1019" spans="1:8">
+    <row r="1019" hidden="1" spans="1:8">
       <c r="A1019" t="s">
         <v>1785</v>
       </c>
@@ -40795,7 +40791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1020" spans="1:8">
+    <row r="1020" hidden="1" spans="1:8">
       <c r="A1020" t="s">
         <v>1785</v>
       </c>
@@ -40821,7 +40817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1021" spans="1:8">
+    <row r="1021" hidden="1" spans="1:8">
       <c r="A1021" t="s">
         <v>1785</v>
       </c>
@@ -40847,7 +40843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1022" spans="1:8">
+    <row r="1022" hidden="1" spans="1:8">
       <c r="A1022" t="s">
         <v>1785</v>
       </c>
@@ -40873,7 +40869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1023" spans="1:8">
+    <row r="1023" hidden="1" spans="1:8">
       <c r="A1023" t="s">
         <v>1785</v>
       </c>
@@ -40899,7 +40895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1024" spans="1:8">
+    <row r="1024" hidden="1" spans="1:8">
       <c r="A1024" t="s">
         <v>1794</v>
       </c>
@@ -40925,7 +40921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1025" spans="1:8">
+    <row r="1025" hidden="1" spans="1:8">
       <c r="A1025" t="s">
         <v>1794</v>
       </c>
@@ -40951,7 +40947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1026" spans="1:8">
+    <row r="1026" hidden="1" spans="1:8">
       <c r="A1026" t="s">
         <v>1795</v>
       </c>
@@ -40977,7 +40973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1027" spans="1:8">
+    <row r="1027" hidden="1" spans="1:8">
       <c r="A1027" t="s">
         <v>1795</v>
       </c>
@@ -41003,7 +40999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1028" spans="1:8">
+    <row r="1028" hidden="1" spans="1:8">
       <c r="A1028" t="s">
         <v>1795</v>
       </c>
@@ -41029,7 +41025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1029" spans="1:8">
+    <row r="1029" hidden="1" spans="1:8">
       <c r="A1029" t="s">
         <v>1795</v>
       </c>
@@ -41055,7 +41051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1030" spans="1:8">
+    <row r="1030" hidden="1" spans="1:8">
       <c r="A1030" t="s">
         <v>1800</v>
       </c>
@@ -41081,7 +41077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1031" spans="1:8">
+    <row r="1031" hidden="1" spans="1:8">
       <c r="A1031" t="s">
         <v>1800</v>
       </c>
@@ -41107,7 +41103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1032" spans="1:8">
+    <row r="1032" hidden="1" spans="1:8">
       <c r="A1032" t="s">
         <v>1800</v>
       </c>
@@ -41133,7 +41129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1033" spans="1:8">
+    <row r="1033" hidden="1" spans="1:8">
       <c r="A1033" t="s">
         <v>1800</v>
       </c>
@@ -41159,7 +41155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1034" spans="1:8">
+    <row r="1034" hidden="1" spans="1:8">
       <c r="A1034" t="s">
         <v>1806</v>
       </c>
@@ -41185,7 +41181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1035" spans="1:8">
+    <row r="1035" hidden="1" spans="1:8">
       <c r="A1035" t="s">
         <v>1806</v>
       </c>
@@ -41211,7 +41207,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1036" spans="1:8">
+    <row r="1036" hidden="1" spans="1:8">
       <c r="A1036" t="s">
         <v>1806</v>
       </c>
@@ -41237,7 +41233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1037" spans="1:8">
+    <row r="1037" hidden="1" spans="1:8">
       <c r="A1037" t="s">
         <v>1811</v>
       </c>
@@ -41263,7 +41259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1038" spans="1:8">
+    <row r="1038" hidden="1" spans="1:8">
       <c r="A1038" t="s">
         <v>1811</v>
       </c>
@@ -41289,7 +41285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1039" spans="1:8">
+    <row r="1039" hidden="1" spans="1:8">
       <c r="A1039" t="s">
         <v>1815</v>
       </c>
@@ -41315,7 +41311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1040" spans="1:8">
+    <row r="1040" hidden="1" spans="1:8">
       <c r="A1040" t="s">
         <v>1815</v>
       </c>
@@ -41341,7 +41337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1041" spans="1:8">
+    <row r="1041" hidden="1" spans="1:8">
       <c r="A1041" t="s">
         <v>1815</v>
       </c>
@@ -41367,7 +41363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1042" spans="1:8">
+    <row r="1042" hidden="1" spans="1:8">
       <c r="A1042" t="s">
         <v>1816</v>
       </c>
@@ -41393,7 +41389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1043" spans="1:8">
+    <row r="1043" hidden="1" spans="1:8">
       <c r="A1043" t="s">
         <v>1816</v>
       </c>
@@ -41419,7 +41415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1044" spans="1:8">
+    <row r="1044" hidden="1" spans="1:8">
       <c r="A1044" t="s">
         <v>1816</v>
       </c>
@@ -41445,7 +41441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1045" spans="1:8">
+    <row r="1045" hidden="1" spans="1:8">
       <c r="A1045" t="s">
         <v>1816</v>
       </c>
@@ -41471,7 +41467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1046" spans="1:8">
+    <row r="1046" hidden="1" spans="1:8">
       <c r="A1046" t="s">
         <v>1816</v>
       </c>
@@ -41497,7 +41493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1047" spans="1:8">
+    <row r="1047" hidden="1" spans="1:8">
       <c r="A1047" t="s">
         <v>1816</v>
       </c>
@@ -41523,7 +41519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1048" spans="1:8">
+    <row r="1048" hidden="1" spans="1:8">
       <c r="A1048" t="s">
         <v>1816</v>
       </c>
@@ -41549,7 +41545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1049" spans="1:8">
+    <row r="1049" hidden="1" spans="1:8">
       <c r="A1049" t="s">
         <v>1816</v>
       </c>
@@ -41575,7 +41571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1050" spans="1:8">
+    <row r="1050" hidden="1" spans="1:8">
       <c r="A1050" t="s">
         <v>1816</v>
       </c>
@@ -41601,7 +41597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1051" spans="1:8">
+    <row r="1051" hidden="1" spans="1:8">
       <c r="A1051" t="s">
         <v>1816</v>
       </c>
@@ -41627,7 +41623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1052" spans="1:8">
+    <row r="1052" hidden="1" spans="1:8">
       <c r="A1052" t="s">
         <v>1828</v>
       </c>
@@ -41653,7 +41649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1053" spans="1:8">
+    <row r="1053" hidden="1" spans="1:8">
       <c r="A1053" t="s">
         <v>1828</v>
       </c>
@@ -41679,7 +41675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1054" spans="1:8">
+    <row r="1054" hidden="1" spans="1:8">
       <c r="A1054" t="s">
         <v>1828</v>
       </c>
@@ -41705,7 +41701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1055" spans="1:8">
+    <row r="1055" hidden="1" spans="1:8">
       <c r="A1055" t="s">
         <v>1828</v>
       </c>
@@ -41731,7 +41727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1056" spans="1:8">
+    <row r="1056" hidden="1" spans="1:8">
       <c r="A1056" t="s">
         <v>1834</v>
       </c>
@@ -41757,7 +41753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1057" spans="1:8">
+    <row r="1057" hidden="1" spans="1:8">
       <c r="A1057" t="s">
         <v>1834</v>
       </c>
@@ -41783,7 +41779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1058" spans="1:8">
+    <row r="1058" hidden="1" spans="1:8">
       <c r="A1058" t="s">
         <v>1834</v>
       </c>
@@ -41809,7 +41805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1059" spans="1:8">
+    <row r="1059" hidden="1" spans="1:8">
       <c r="A1059" t="s">
         <v>1834</v>
       </c>
@@ -41835,7 +41831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1060" spans="1:8">
+    <row r="1060" hidden="1" spans="1:8">
       <c r="A1060" t="s">
         <v>1834</v>
       </c>
@@ -41861,7 +41857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1061" spans="1:8">
+    <row r="1061" hidden="1" spans="1:8">
       <c r="A1061" t="s">
         <v>1835</v>
       </c>
@@ -41887,7 +41883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1062" spans="1:8">
+    <row r="1062" hidden="1" spans="1:8">
       <c r="A1062" t="s">
         <v>1835</v>
       </c>
@@ -41913,7 +41909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1063" spans="1:8">
+    <row r="1063" hidden="1" spans="1:8">
       <c r="A1063" t="s">
         <v>1835</v>
       </c>
@@ -41939,7 +41935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1064" spans="1:8">
+    <row r="1064" hidden="1" spans="1:8">
       <c r="A1064" t="s">
         <v>1835</v>
       </c>
@@ -41965,7 +41961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1065" spans="1:8">
+    <row r="1065" hidden="1" spans="1:8">
       <c r="A1065" t="s">
         <v>1835</v>
       </c>
@@ -41991,7 +41987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1066" spans="1:8">
+    <row r="1066" hidden="1" spans="1:8">
       <c r="A1066" t="s">
         <v>1841</v>
       </c>
@@ -42017,7 +42013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1067" spans="1:8">
+    <row r="1067" hidden="1" spans="1:8">
       <c r="A1067" t="s">
         <v>1841</v>
       </c>
@@ -42043,7 +42039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1068" spans="1:8">
+    <row r="1068" hidden="1" spans="1:8">
       <c r="A1068" t="s">
         <v>1841</v>
       </c>
@@ -42069,7 +42065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1069" spans="1:8">
+    <row r="1069" hidden="1" spans="1:8">
       <c r="A1069" t="s">
         <v>1841</v>
       </c>
@@ -42095,7 +42091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1070" spans="1:8">
+    <row r="1070" hidden="1" spans="1:8">
       <c r="A1070" t="s">
         <v>1841</v>
       </c>
@@ -42121,7 +42117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1071" spans="1:8">
+    <row r="1071" hidden="1" spans="1:8">
       <c r="A1071" t="s">
         <v>1842</v>
       </c>
@@ -42147,7 +42143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1072" spans="1:8">
+    <row r="1072" hidden="1" spans="1:8">
       <c r="A1072" t="s">
         <v>1842</v>
       </c>
@@ -42173,7 +42169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1073" spans="1:8">
+    <row r="1073" hidden="1" spans="1:8">
       <c r="A1073" t="s">
         <v>1842</v>
       </c>
@@ -42199,7 +42195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1074" spans="1:8">
+    <row r="1074" hidden="1" spans="1:8">
       <c r="A1074" t="s">
         <v>1842</v>
       </c>
@@ -42227,6 +42223,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1074" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CVE-2024-3332"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
